--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="27">
   <si>
     <t xml:space="preserve">AttackDamage:200|AttackInterval:-50</t>
   </si>

--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -511,7 +511,7 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
     <col min="1" max="1" width="20.2109375" style="1" bestFit="1" customWidth="1"/>
@@ -533,54 +533,66 @@
         </is>
       </c>
       <c r="B1" s="0" t="inlineStr">
+        <v>name</v>
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <v>description</v>
+        <is>
+          <t xml:space="preserve">description</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
         <v>skill_type</v>
         <is>
           <t xml:space="preserve">skill_type</t>
         </is>
       </c>
-      <c r="C1" s="0" t="inlineStr">
+      <c r="E1" s="0" t="inlineStr">
         <v>skill_cooldown</v>
         <is>
           <t xml:space="preserve">skill_cooldown</t>
         </is>
       </c>
-      <c r="D1" s="0" t="inlineStr">
+      <c r="F1" s="0" t="inlineStr">
         <v>skill_icon_id</v>
         <is>
           <t xml:space="preserve">skill_icon_id</t>
         </is>
       </c>
-      <c r="E1" s="0" t="inlineStr">
+      <c r="G1" s="0" t="inlineStr">
         <v>skill_projectile_prefab_id</v>
         <is>
           <t xml:space="preserve">skill_projectile_prefab_id</t>
         </is>
       </c>
-      <c r="F1" s="0" t="inlineStr">
+      <c r="H1" s="0" t="inlineStr">
         <v>skill_projectile_damage</v>
         <is>
           <t xml:space="preserve">skill_projectile_damage</t>
         </is>
       </c>
-      <c r="G1" s="0" t="inlineStr">
+      <c r="I1" s="0" t="inlineStr">
         <v>skill_projectile_range</v>
         <is>
           <t xml:space="preserve">skill_projectile_range</t>
         </is>
       </c>
-      <c r="H1" s="0" t="inlineStr">
+      <c r="J1" s="0" t="inlineStr">
         <v>skill_projectile_count</v>
         <is>
           <t xml:space="preserve">skill_projectile_count</t>
         </is>
       </c>
-      <c r="I1" s="0" t="inlineStr">
+      <c r="K1" s="0" t="inlineStr">
         <v>skill_buff_duration</v>
         <is>
           <t xml:space="preserve">skill_buff_duration</t>
         </is>
       </c>
-      <c r="J1" s="0" t="inlineStr">
+      <c r="L1" s="0" t="inlineStr">
         <v>skill_buffs</v>
         <is>
           <t xml:space="preserve">skill_buffs</t>
@@ -597,25 +609,37 @@
       <c r="B2" s="0" t="inlineStr">
         <v/>
         <is>
+          <t xml:space="preserve">속사 모드</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">5초간 공격 간격 50% 감소</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <v/>
+        <is>
           <t xml:space="preserve">SelfBuff</t>
         </is>
       </c>
-      <c r="C2" s="0">
+      <c r="E2" s="0">
         <v>20</v>
       </c>
-      <c r="F2" s="0">
-        <v>0</v>
-      </c>
-      <c r="G2" s="0">
-        <v>0</v>
-      </c>
       <c r="H2" s="0">
         <v>0</v>
       </c>
       <c r="I2" s="0">
+        <v>0</v>
+      </c>
+      <c r="J2" s="0">
+        <v>0</v>
+      </c>
+      <c r="K2" s="0">
         <v>5</v>
       </c>
-      <c r="J2" s="0" t="inlineStr">
+      <c r="L2" s="0" t="inlineStr">
         <v/>
         <is>
           <t xml:space="preserve">AttackInterval:-50</t>
@@ -632,27 +656,39 @@
       <c r="B3" s="0" t="inlineStr">
         <v/>
         <is>
+          <t xml:space="preserve">화력 집중</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">6초간 공격력 100% 증가</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <v/>
+        <is>
           <t xml:space="preserve">SelfBuff</t>
         </is>
       </c>
-      <c r="C3" s="0">
+      <c r="E3" s="0">
         <v>25</v>
       </c>
-      <c r="D3" s="0" t="inlineStr"/>
-      <c r="E3" s="0" t="inlineStr"/>
-      <c r="F3" s="0">
-        <v>0</v>
-      </c>
-      <c r="G3" s="0">
-        <v>0</v>
-      </c>
+      <c r="F3" s="0" t="inlineStr"/>
+      <c r="G3" s="0" t="inlineStr"/>
       <c r="H3" s="0">
         <v>0</v>
       </c>
       <c r="I3" s="0">
+        <v>0</v>
+      </c>
+      <c r="J3" s="0">
+        <v>0</v>
+      </c>
+      <c r="K3" s="0">
         <v>6</v>
       </c>
-      <c r="J3" s="0" t="inlineStr">
+      <c r="L3" s="0" t="inlineStr">
         <v/>
         <is>
           <t xml:space="preserve">AttackDamage:100</t>
@@ -669,32 +705,44 @@
       <c r="B4" s="0" t="inlineStr">
         <v/>
         <is>
+          <t xml:space="preserve">미사일 폭격</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">미사일 3발 발사 (피해 200)</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <v/>
+        <is>
           <t xml:space="preserve">Projectile</t>
         </is>
       </c>
-      <c r="C4" s="0">
+      <c r="E4" s="0">
         <v>20</v>
       </c>
-      <c r="D4" s="0" t="inlineStr"/>
-      <c r="E4" s="0" t="inlineStr">
+      <c r="F4" s="0" t="inlineStr"/>
+      <c r="G4" s="0" t="inlineStr">
         <v/>
         <is>
           <t xml:space="preserve">MissileProjectile</t>
         </is>
       </c>
-      <c r="F4" s="0">
+      <c r="H4" s="0">
         <v>200</v>
       </c>
-      <c r="G4" s="0">
+      <c r="I4" s="0">
         <v>15</v>
       </c>
-      <c r="H4" s="0">
+      <c r="J4" s="0">
         <v>3</v>
       </c>
-      <c r="I4" s="0">
-        <v>0</v>
-      </c>
-      <c r="J4" s="0" t="inlineStr"/>
+      <c r="K4" s="0">
+        <v>0</v>
+      </c>
+      <c r="L4" s="0" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
@@ -706,27 +754,39 @@
       <c r="B5" s="0" t="inlineStr">
         <v/>
         <is>
+          <t xml:space="preserve">치명 사격</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">5초간 치명타 확률 50%, 치명타 피해 100% 증가</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <v/>
+        <is>
           <t xml:space="preserve">SelfBuff</t>
         </is>
       </c>
-      <c r="C5" s="0">
+      <c r="E5" s="0">
         <v>30</v>
       </c>
-      <c r="D5" s="0" t="inlineStr"/>
-      <c r="E5" s="0" t="inlineStr"/>
-      <c r="F5" s="0">
-        <v>0</v>
-      </c>
-      <c r="G5" s="0">
-        <v>0</v>
-      </c>
+      <c r="F5" s="0" t="inlineStr"/>
+      <c r="G5" s="0" t="inlineStr"/>
       <c r="H5" s="0">
         <v>0</v>
       </c>
       <c r="I5" s="0">
+        <v>0</v>
+      </c>
+      <c r="J5" s="0">
+        <v>0</v>
+      </c>
+      <c r="K5" s="0">
         <v>5</v>
       </c>
-      <c r="J5" s="0" t="inlineStr">
+      <c r="L5" s="0" t="inlineStr">
         <v/>
         <is>
           <t xml:space="preserve">CriticalChance:50|CriticalDamage:100</t>
@@ -743,28 +803,40 @@
       <c r="B6" s="0" t="inlineStr">
         <v/>
         <is>
+          <t xml:space="preserve">전기 충격</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">전기 투사체 발사 (피해 100, 범위 30)</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <v/>
+        <is>
           <t xml:space="preserve">Projectile</t>
         </is>
       </c>
-      <c r="C6" s="0">
+      <c r="E6" s="0">
         <v>30</v>
       </c>
-      <c r="E6" s="0" t="inlineStr">
+      <c r="G6" s="0" t="inlineStr">
         <v/>
         <is>
           <t xml:space="preserve">ElectrickProjectile</t>
         </is>
       </c>
-      <c r="F6" s="0">
+      <c r="H6" s="0">
         <v>100</v>
       </c>
-      <c r="G6" s="0">
+      <c r="I6" s="0">
         <v>30</v>
       </c>
-      <c r="H6" s="0">
+      <c r="J6" s="0">
         <v>1</v>
       </c>
-      <c r="I6" s="0">
+      <c r="K6" s="0">
         <v>0</v>
       </c>
     </row>
@@ -778,25 +850,37 @@
       <c r="B7" s="0" t="inlineStr">
         <v/>
         <is>
+          <t xml:space="preserve">광폭화</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">5초간 공격력 200% 증가, 공격 간격 50% 감소</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <v/>
+        <is>
           <t xml:space="preserve">SelfBuff</t>
         </is>
       </c>
-      <c r="C7" s="0">
+      <c r="E7" s="0">
         <v>30</v>
       </c>
-      <c r="F7" s="0">
-        <v>0</v>
-      </c>
-      <c r="G7" s="0">
-        <v>0</v>
-      </c>
       <c r="H7" s="0">
         <v>0</v>
       </c>
       <c r="I7" s="0">
+        <v>0</v>
+      </c>
+      <c r="J7" s="0">
+        <v>0</v>
+      </c>
+      <c r="K7" s="0">
         <v>5</v>
       </c>
-      <c r="J7" s="0" t="inlineStr">
+      <c r="L7" s="0" t="inlineStr">
         <v/>
         <is>
           <t xml:space="preserve">AttackDamage:200|AttackInterval:-50</t>
@@ -813,27 +897,39 @@
       <c r="B8" s="0" t="inlineStr">
         <v/>
         <is>
+          <t xml:space="preserve">즉발 사격</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">즉시 강력한 일격을 가한다</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <v/>
+        <is>
           <t xml:space="preserve">InstantAttack</t>
         </is>
       </c>
-      <c r="C8" s="0">
+      <c r="E8" s="0">
         <v>15</v>
       </c>
-      <c r="D8" s="0" t="inlineStr"/>
-      <c r="E8" s="0" t="inlineStr"/>
-      <c r="F8" s="0">
-        <v>0</v>
-      </c>
-      <c r="G8" s="0">
-        <v>0</v>
-      </c>
+      <c r="F8" s="0" t="inlineStr"/>
+      <c r="G8" s="0" t="inlineStr"/>
       <c r="H8" s="0">
         <v>0</v>
       </c>
       <c r="I8" s="0">
         <v>0</v>
       </c>
-      <c r="J8" s="0" t="inlineStr"/>
+      <c r="J8" s="0">
+        <v>0</v>
+      </c>
+      <c r="K8" s="0">
+        <v>0</v>
+      </c>
+      <c r="L8" s="0" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
@@ -845,22 +941,34 @@
       <c r="B9" s="0" t="inlineStr">
         <v/>
         <is>
+          <t xml:space="preserve">즉발 폭발</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">즉시 주변에 폭발을 일으킨다</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <v/>
+        <is>
           <t xml:space="preserve">InstantAttack</t>
         </is>
       </c>
-      <c r="C9" s="0">
+      <c r="E9" s="0">
         <v>20</v>
       </c>
-      <c r="F9" s="0">
-        <v>0</v>
-      </c>
-      <c r="G9" s="0">
-        <v>0</v>
-      </c>
       <c r="H9" s="0">
         <v>0</v>
       </c>
       <c r="I9" s="0">
+        <v>0</v>
+      </c>
+      <c r="J9" s="0">
+        <v>0</v>
+      </c>
+      <c r="K9" s="0">
         <v>0</v>
       </c>
     </row>
@@ -874,25 +982,37 @@
       <c r="B10" s="0" t="inlineStr">
         <v/>
         <is>
+          <t xml:space="preserve">광역 탐지</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">15초간 공격 범위 300% 증가</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <v/>
+        <is>
           <t xml:space="preserve">SelfBuff</t>
         </is>
       </c>
-      <c r="C10" s="0">
+      <c r="E10" s="0">
         <v>30</v>
       </c>
-      <c r="F10" s="0">
-        <v>0</v>
-      </c>
-      <c r="G10" s="0">
-        <v>0</v>
-      </c>
       <c r="H10" s="0">
         <v>0</v>
       </c>
       <c r="I10" s="0">
+        <v>0</v>
+      </c>
+      <c r="J10" s="0">
+        <v>0</v>
+      </c>
+      <c r="K10" s="0">
         <v>15</v>
       </c>
-      <c r="J10" s="0" t="inlineStr">
+      <c r="L10" s="0" t="inlineStr">
         <v/>
         <is>
           <t xml:space="preserve">AttackRange:300</t>
@@ -911,7 +1031,7 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -922,27 +1042,39 @@
         </is>
       </c>
       <c r="B1" s="0" t="inlineStr">
+        <v>name</v>
+        <is>
+          <t xml:space="preserve">name</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
         <v>passive_type</v>
         <is>
           <t xml:space="preserve">passive_type</t>
         </is>
       </c>
-      <c r="C1" s="0" t="inlineStr">
+      <c r="D1" s="0" t="inlineStr">
         <v>param1</v>
         <is>
           <t xml:space="preserve">param1</t>
         </is>
       </c>
-      <c r="D1" s="0" t="inlineStr">
+      <c r="E1" s="0" t="inlineStr">
         <v>param2</v>
         <is>
           <t xml:space="preserve">param2</t>
         </is>
       </c>
-      <c r="E1" s="0" t="inlineStr">
+      <c r="F1" s="0" t="inlineStr">
         <v>param3</v>
         <is>
           <t xml:space="preserve">param3</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <v>description</v>
+        <is>
+          <t xml:space="preserve">description</t>
         </is>
       </c>
     </row>
@@ -956,22 +1088,34 @@
       <c r="B2" s="0" t="inlineStr">
         <v/>
         <is>
+          <t xml:space="preserve">폭발탄</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <v/>
+        <is>
           <t xml:space="preserve">OverrideEveryN</t>
         </is>
       </c>
-      <c r="C2" s="0" t="inlineStr">
+      <c r="D2" s="0" t="inlineStr">
         <v/>
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="D2" s="0" t="inlineStr">
+      <c r="E2" s="0" t="inlineStr">
         <v/>
         <is>
           <t xml:space="preserve">ExplosionProjectile</t>
         </is>
       </c>
-      <c r="E2" s="0" t="inlineStr"/>
+      <c r="F2" s="0" t="inlineStr"/>
+      <c r="G2" s="0" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">5회 공격마다 폭발 투사체 발사</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
@@ -983,22 +1127,34 @@
       <c r="B3" s="0" t="inlineStr">
         <v/>
         <is>
+          <t xml:space="preserve">화염 장판</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <v/>
+        <is>
           <t xml:space="preserve">OverrideEveryN</t>
         </is>
       </c>
-      <c r="C3" s="0" t="inlineStr">
+      <c r="D3" s="0" t="inlineStr">
         <v/>
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="D3" s="0" t="inlineStr">
+      <c r="E3" s="0" t="inlineStr">
         <v/>
         <is>
           <t xml:space="preserve">FireAreaProjectile</t>
         </is>
       </c>
-      <c r="E3" s="0" t="inlineStr"/>
+      <c r="F3" s="0" t="inlineStr"/>
+      <c r="G3" s="0" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">3회 공격마다 화염 장판 투사체 발사</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
@@ -1010,22 +1166,34 @@
       <c r="B4" s="0" t="inlineStr">
         <v/>
         <is>
+          <t xml:space="preserve">연사</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <v/>
+        <is>
           <t xml:space="preserve">RepeatAfterAttack</t>
         </is>
       </c>
-      <c r="C4" s="0" t="inlineStr">
+      <c r="D4" s="0" t="inlineStr">
         <v/>
         <is>
           <t xml:space="preserve">0.5</t>
         </is>
       </c>
-      <c r="D4" s="0" t="inlineStr">
+      <c r="E4" s="0" t="inlineStr">
         <v/>
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="E4" s="0" t="inlineStr"/>
+      <c r="F4" s="0" t="inlineStr"/>
+      <c r="G4" s="0" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">공격 후 0.5초 뒤 1회 추가 발사</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
@@ -1037,22 +1205,34 @@
       <c r="B5" s="0" t="inlineStr">
         <v/>
         <is>
+          <t xml:space="preserve">속사</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <v/>
+        <is>
           <t xml:space="preserve">RepeatAfterAttack</t>
         </is>
       </c>
-      <c r="C5" s="0" t="inlineStr">
+      <c r="D5" s="0" t="inlineStr">
         <v/>
         <is>
           <t xml:space="preserve">0.2</t>
         </is>
       </c>
-      <c r="D5" s="0" t="inlineStr">
+      <c r="E5" s="0" t="inlineStr">
         <v/>
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="E5" s="0" t="inlineStr"/>
+      <c r="F5" s="0" t="inlineStr"/>
+      <c r="G5" s="0" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">공격 후 0.2초 간격으로 2회 추가 발사</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
@@ -1064,17 +1244,29 @@
       <c r="B6" s="0" t="inlineStr">
         <v/>
         <is>
+          <t xml:space="preserve">연쇄 공격</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <v/>
+        <is>
           <t xml:space="preserve">ChainAttackChance</t>
         </is>
       </c>
-      <c r="C6" s="0" t="inlineStr">
+      <c r="D6" s="0" t="inlineStr">
         <v/>
         <is>
           <t xml:space="preserve">20</t>
         </is>
       </c>
-      <c r="D6" s="0" t="inlineStr"/>
       <c r="E6" s="0" t="inlineStr"/>
+      <c r="F6" s="0" t="inlineStr"/>
+      <c r="G6" s="0" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">20% 확률로 추가 공격</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
@@ -1086,25 +1278,37 @@
       <c r="B7" s="0" t="inlineStr">
         <v/>
         <is>
+          <t xml:space="preserve">무차별 폭격</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <v/>
+        <is>
           <t xml:space="preserve">RandomPosBombard</t>
         </is>
       </c>
-      <c r="C7" s="0" t="inlineStr">
+      <c r="D7" s="0" t="inlineStr">
         <v/>
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="D7" s="0" t="inlineStr">
+      <c r="E7" s="0" t="inlineStr">
         <v/>
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="E7" s="0" t="inlineStr">
+      <c r="F7" s="0" t="inlineStr">
         <v/>
         <is>
           <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="G7" s="0" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">공격 시 무작위 위치에 1발 추가 폭격</t>
         </is>
       </c>
     </row>
@@ -1118,17 +1322,29 @@
       <c r="B8" s="0" t="inlineStr">
         <v/>
         <is>
+          <t xml:space="preserve">강화 연쇄 공격</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <v/>
+        <is>
           <t xml:space="preserve">ChainAttackChance</t>
         </is>
       </c>
-      <c r="C8" s="0" t="inlineStr">
+      <c r="D8" s="0" t="inlineStr">
         <v/>
         <is>
           <t xml:space="preserve">30</t>
         </is>
       </c>
-      <c r="D8" s="0" t="inlineStr"/>
       <c r="E8" s="0" t="inlineStr"/>
+      <c r="F8" s="0" t="inlineStr"/>
+      <c r="G8" s="0" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">30% 확률로 추가 공격</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
@@ -1140,25 +1356,37 @@
       <c r="B9" s="0" t="inlineStr">
         <v/>
         <is>
+          <t xml:space="preserve">후폭발</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <v/>
+        <is>
           <t xml:space="preserve">FollowUpExplosion</t>
         </is>
       </c>
-      <c r="C9" s="0" t="inlineStr">
+      <c r="D9" s="0" t="inlineStr">
         <v/>
         <is>
           <t xml:space="preserve">0.2</t>
         </is>
       </c>
-      <c r="D9" s="0" t="inlineStr">
+      <c r="E9" s="0" t="inlineStr">
         <v/>
         <is>
           <t xml:space="preserve">ExplosionProjectile</t>
         </is>
       </c>
-      <c r="E9" s="0" t="inlineStr">
+      <c r="F9" s="0" t="inlineStr">
         <v/>
         <is>
           <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="G9" s="0" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">공격 후 0.2초 뒤 반경 3의 폭발 생성</t>
         </is>
       </c>
     </row>
@@ -1172,25 +1400,37 @@
       <c r="B10" s="0" t="inlineStr">
         <v/>
         <is>
+          <t xml:space="preserve">냉기 방출</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <v/>
+        <is>
           <t xml:space="preserve">PeriodicSpawn</t>
         </is>
       </c>
-      <c r="C10" s="0" t="inlineStr">
+      <c r="D10" s="0" t="inlineStr">
         <v/>
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="D10" s="0" t="inlineStr">
+      <c r="E10" s="0" t="inlineStr">
         <v/>
         <is>
           <t xml:space="preserve">ColdAirProjectile</t>
         </is>
       </c>
-      <c r="E10" s="0" t="inlineStr">
+      <c r="F10" s="0" t="inlineStr">
         <v/>
         <is>
           <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="G10" s="0" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">3초마다 반경 5의 냉기 투사체 발사</t>
         </is>
       </c>
     </row>

--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -1,21 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="HCell" lastEdited="11.0" lowestEdited="11.0" rupBuild="0.2292"/>
-  <workbookPr codeName="ThisWorkbook" autoCompressPictures="1"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28545" windowHeight="11700" activeTab="1"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="active_skill_data" sheetId="1" r:id="rId4"/>
-    <sheet name="passive_skill_data" sheetId="2" r:id="rId5"/>
+    <sheet name="active_skill_data" sheetId="1" r:id="rId1"/>
+    <sheet name="passive_skill_data" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr/>
+  <fileRecoveryPr autoRecover="0" crashSave="0" dataExtractLoad="0" repairLoad="1"/>
+  <extLst>
+    <ext uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="97">
   <si>
     <t xml:space="preserve">1</t>
   </si>
@@ -313,36 +319,17 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
+      <sz val="8"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="2">
@@ -355,18 +342,11 @@
   </fills>
   <borders count="1">
     <border>
-      <left>
-        <color indexed="64"/>
-      </left>
-      <right>
-        <color indexed="64"/>
-      </right>
-      <top>
-        <color indexed="64"/>
-      </top>
-      <bottom>
-        <color indexed="64"/>
-      </bottom>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -381,15 +361,44 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf/>
+  <dxfs count="7">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFAEBFEA"/>
+          <bgColor rgb="FFAEBFEA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFAEBFEA"/>
+          <bgColor rgb="FFAEBFEA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF94A5DF"/>
+          <bgColor rgb="FF94A5DF"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color rgb="FF6182D6"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF6182D6"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -422,30 +431,36 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF6182D6"/>
+          <bgColor rgb="FF6182D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="9">
-      <tableStyleElement type="wholeTable" size="1"/>
-      <tableStyleElement type="headerRow" size="1" dxfId="5"/>
-      <tableStyleElement type="totalRow" size="1" dxfId="4"/>
-      <tableStyleElement type="firstColumn" size="1" dxfId="3"/>
-      <tableStyleElement type="lastColumn" size="1" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" size="1" dxfId="2"/>
-      <tableStyleElement type="secondRowStripe" size="1" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" size="1" dxfId="2"/>
-      <tableStyleElement type="secondColumnStripe" size="1" dxfId="1"/>
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="0" count="6">
+      <tableStyleElement type="firstColumn" dxfId="6"/>
+      <tableStyleElement type="lastColumn" dxfId="5"/>
+      <tableStyleElement type="firstRowStripe" dxfId="4"/>
+      <tableStyleElement type="secondRowStripe" dxfId="3"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="2"/>
+      <tableStyleElement type="secondColumnStripe" dxfId="1"/>
     </tableStyle>
-    <tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="8">
-      <tableStyleElement type="wholeTable" size="1" dxfId="6"/>
-      <tableStyleElement type="headerRow" size="1" dxfId="11"/>
-      <tableStyleElement type="totalRow" size="1" dxfId="10"/>
-      <tableStyleElement type="firstColumn" size="1" dxfId="9"/>
-      <tableStyleElement type="lastColumn" size="1" dxfId="9"/>
-      <tableStyleElement type="firstRowStripe" size="1" dxfId="7"/>
-      <tableStyleElement type="secondRowStripe" size="1" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" size="1" dxfId="8"/>
+    <tableStyle name="Light Style 1 - Accent 1" pivot="0" table="0" count="1">
+      <tableStyleElement type="secondRowStripe"/>
     </tableStyle>
   </tableStyles>
+  <extLst>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -727,6 +742,8 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -734,12 +751,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:M10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
     <col min="1" max="1" width="20.2109375" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.2734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.78515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.78515625" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.78515625" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="18.7109375" style="2" bestFit="1" customWidth="1"/>
@@ -747,7 +764,7 @@
     <col min="10" max="10" width="32.5" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A1" s="1" t="s">
         <v>51</v>
       </c>
@@ -785,7 +802,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A2" s="1" t="s">
         <v>18</v>
       </c>
@@ -817,7 +834,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -851,7 +868,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
@@ -885,7 +902,7 @@
       </c>
       <c r="L4" s="1"/>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A5" s="1" t="s">
         <v>22</v>
       </c>
@@ -919,7 +936,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -951,7 +968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A7" s="1" t="s">
         <v>35</v>
       </c>
@@ -983,7 +1000,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A8" s="1" t="s">
         <v>38</v>
       </c>
@@ -1015,7 +1032,7 @@
       </c>
       <c r="L8" s="1"/>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A9" s="1" t="s">
         <v>27</v>
       </c>
@@ -1044,7 +1061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.55">
       <c r="A10" s="1" t="s">
         <v>36</v>
       </c>
@@ -1077,6 +1094,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.699861109256744" right="0.699861109256744" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
 </worksheet>
@@ -1086,16 +1104,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="16.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.6" x14ac:dyDescent="0.55"/>
   <cols>
-    <col min="2" max="2" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.10546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.00390625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.20703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="32.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.0703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.2109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="32.92578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A1" s="1" t="s">
         <v>51</v>
       </c>
@@ -1118,7 +1136,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -1139,7 +1157,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -1160,7 +1178,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A4" s="1" t="s">
         <v>28</v>
       </c>
@@ -1181,7 +1199,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A5" s="1" t="s">
         <v>37</v>
       </c>
@@ -1192,7 +1210,7 @@
         <v>57</v>
       </c>
       <c r="D5" s="1">
-        <v>0.20000000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="E5" s="1">
         <v>3</v>
@@ -1202,7 +1220,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A6" s="1" t="s">
         <v>29</v>
       </c>
@@ -1221,7 +1239,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A7" s="1" t="s">
         <v>31</v>
       </c>
@@ -1244,7 +1262,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A8" s="1" t="s">
         <v>34</v>
       </c>
@@ -1263,7 +1281,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A9" s="1" t="s">
         <v>40</v>
       </c>
@@ -1286,7 +1304,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.55">
       <c r="A10" s="1" t="s">
         <v>30</v>
       </c>
@@ -1310,6 +1328,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
 </worksheet>

--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="77">
   <si>
     <t xml:space="preserve">skill_projectile_count</t>
   </si>

--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="77">
   <si>
     <t xml:space="preserve">skill_projectile_count</t>
   </si>

--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -1,43 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="active_skill_data" sheetId="1" r:id="rId1"/>
-    <sheet name="passive_skill_data" sheetId="2" r:id="rId2"/>
+    <sheet name="active_skill_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="passive_skill_data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
   <fonts count="3">
     <font>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
+      <name val="돋움"/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="8"/>
-      <name val="돋움"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
   </fonts>
   <fills count="8">
@@ -99,80 +96,80 @@
     </xf>
   </cellStyleXfs>
   <cellXfs count="26">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -198,17 +195,17 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
       </font>
       <border>
         <top style="thin">
@@ -218,7 +215,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
       </font>
       <border>
         <bottom style="medium">
@@ -261,7 +258,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color rgb="FFFFFFFF"/>
       </font>
       <fill>
@@ -273,7 +270,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color rgb="FFFFFFFF"/>
       </font>
       <fill>
@@ -285,7 +282,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color rgb="FFFFFFFF"/>
       </font>
       <fill>
@@ -302,7 +299,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color rgb="FFFFFFFF"/>
       </font>
       <fill>
@@ -656,844 +653,782 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="Sheet1">
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
-    <col min="1" max="1" width="20.2109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="49.78515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.28515625" style="3" customWidth="1"/>
-    <col min="12" max="12" width="17.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col width="20.2109375" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
+    <col width="12.28515625" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
+    <col width="49.78515625" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
+    <col width="12.28515625" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
+    <col width="13.42578125" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
+    <col width="10.85546875" bestFit="1" customWidth="1" style="3" min="6" max="6"/>
+    <col width="22" bestFit="1" customWidth="1" style="3" min="7" max="7"/>
+    <col width="21" bestFit="1" customWidth="1" style="3" min="8" max="8"/>
+    <col width="18.85546875" bestFit="1" customWidth="1" style="3" min="9" max="9"/>
+    <col width="18.7109375" bestFit="1" customWidth="1" style="3" min="10" max="10"/>
+    <col width="16.28515625" customWidth="1" style="3" min="11" max="11"/>
+    <col width="17.42578125" bestFit="1" customWidth="1" style="3" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="inlineStr">
-        <v>id</v>
-        <is>
-          <t xml:space="preserve">id</t>
+        <is>
+          <t>id</t>
         </is>
       </c>
       <c r="B1" s="21" t="inlineStr">
-        <v>name</v>
-        <is>
-          <t xml:space="preserve">name</t>
+        <is>
+          <t>name</t>
         </is>
       </c>
       <c r="C1" s="21" t="inlineStr">
-        <v>description</v>
-        <is>
-          <t xml:space="preserve">description</t>
+        <is>
+          <t>description</t>
         </is>
       </c>
       <c r="D1" s="21" t="inlineStr">
-        <v>skill_type</v>
-        <is>
-          <t xml:space="preserve">skill_type</t>
+        <is>
+          <t>skill_type</t>
         </is>
       </c>
       <c r="E1" s="21" t="inlineStr">
-        <v>skill_cooldown</v>
-        <is>
-          <t xml:space="preserve">skill_cooldown</t>
+        <is>
+          <t>skill_cooldown</t>
         </is>
       </c>
       <c r="F1" s="21" t="inlineStr">
-        <v>skill_icon_id</v>
-        <is>
-          <t xml:space="preserve">skill_icon_id</t>
+        <is>
+          <t>skill_icon_id</t>
         </is>
       </c>
       <c r="G1" s="21" t="inlineStr">
-        <v>skill_projectile_prefab_id</v>
-        <is>
-          <t xml:space="preserve">skill_projectile_prefab_id</t>
+        <is>
+          <t>skill_projectile_prefab_id</t>
         </is>
       </c>
       <c r="H1" s="21" t="inlineStr">
-        <v>skill_projectile_damage</v>
-        <is>
-          <t xml:space="preserve">skill_projectile_damage</t>
+        <is>
+          <t>skill_projectile_damage</t>
         </is>
       </c>
       <c r="I1" s="21" t="inlineStr">
-        <v>skill_projectile_range</v>
-        <is>
-          <t xml:space="preserve">skill_projectile_range</t>
+        <is>
+          <t>skill_projectile_range</t>
         </is>
       </c>
       <c r="J1" s="21" t="inlineStr">
-        <v>skill_projectile_count</v>
-        <is>
-          <t xml:space="preserve">skill_projectile_count</t>
+        <is>
+          <t>skill_projectile_count</t>
         </is>
       </c>
       <c r="K1" s="21" t="inlineStr">
-        <v>skill_buff_duration</v>
-        <is>
-          <t xml:space="preserve">skill_buff_duration</t>
+        <is>
+          <t>skill_buff_duration</t>
         </is>
       </c>
       <c r="L1" s="21" t="inlineStr">
-        <v>skill_buffs</v>
-        <is>
-          <t xml:space="preserve">skill_buffs</t>
+        <is>
+          <t>skill_buffs</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="21">
+      <c r="A2" s="21" t="n">
         <v>50001</v>
       </c>
       <c r="B2" s="21" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">속사 모드</t>
+        <is>
+          <t>속사 모드</t>
         </is>
       </c>
       <c r="C2" s="21" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">5초간 공격 간격 50% 감소</t>
+        <is>
+          <t>5초간 공격 간격 50% 감소</t>
         </is>
       </c>
       <c r="D2" s="21" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">SelfBuff</t>
-        </is>
-      </c>
-      <c r="E2" s="21">
+        <is>
+          <t>SelfBuff</t>
+        </is>
+      </c>
+      <c r="E2" s="21" t="n">
         <v>20</v>
       </c>
-      <c r="H2" s="21">
+      <c r="H2" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="21">
+      <c r="I2" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="21">
+      <c r="J2" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="K2" s="21">
+      <c r="K2" s="21" t="n">
         <v>5</v>
       </c>
       <c r="L2" s="21" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">AttackInterval:-50</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" s="11" customFormat="1">
-      <c r="A3" s="14">
+        <is>
+          <t>AttackInterval:-50</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" customFormat="1" s="11">
+      <c r="A3" s="14" t="n">
         <v>50003</v>
       </c>
       <c r="B3" s="13" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">블리자드</t>
+        <is>
+          <t>블리자드</t>
         </is>
       </c>
       <c r="C3" s="13" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">15초 동안 범위가 맵을 덮을 정도로 넓어짐</t>
-        </is>
-      </c>
-      <c r="D3" s="14"/>
-      <c r="E3" s="13">
+        <is>
+          <t>15초 동안 범위가 맵을 덮을 정도로 넓어짐</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="n"/>
+      <c r="E3" s="13" t="n">
         <v>30</v>
       </c>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14">
+      <c r="F3" s="14" t="n"/>
+      <c r="G3" s="14" t="n"/>
+      <c r="H3" s="14" t="n"/>
+      <c r="I3" s="14" t="n"/>
+      <c r="J3" s="14" t="n"/>
+      <c r="K3" s="14" t="n">
         <v>15</v>
       </c>
-      <c r="L3" s="14"/>
-    </row>
-    <row r="4" s="14" customFormat="1">
-      <c r="A4" s="21">
+      <c r="L3" s="14" t="n"/>
+    </row>
+    <row r="4" customFormat="1" s="14">
+      <c r="A4" s="21" t="n">
         <v>50004</v>
       </c>
       <c r="B4" s="21" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">즉발 폭발</t>
+        <is>
+          <t>즉발 폭발</t>
         </is>
       </c>
       <c r="C4" s="21" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">즉시 주변에 폭발을 일으킨다</t>
+        <is>
+          <t>즉시 주변에 폭발을 일으킨다</t>
         </is>
       </c>
       <c r="D4" s="21" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">InstantAttack</t>
-        </is>
-      </c>
-      <c r="E4" s="21">
+        <is>
+          <t>InstantAttack</t>
+        </is>
+      </c>
+      <c r="E4" s="21" t="n">
         <v>20</v>
       </c>
-      <c r="H4" s="21">
+      <c r="H4" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="21">
+      <c r="I4" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="21">
+      <c r="J4" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="K4" s="21">
+      <c r="K4" s="21" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="5" s="21" customFormat="1">
+    <row r="5" customFormat="1" s="21">
       <c r="A5" s="21" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">50005</t>
+        <is>
+          <t>50005</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">전기 충격</t>
+        <is>
+          <t>전기 충격</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">하늘에서 번개가 떨어져 넓은 원형 범위에 피해를 준다.</t>
+        <is>
+          <t>하늘에서 번개가 떨어져 넓은 원형 범위에 피해를 준다.</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Projectile</t>
-        </is>
-      </c>
-      <c r="E5" s="21">
+        <is>
+          <t>Projectile</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="n">
         <v>30</v>
       </c>
-      <c r="G5" s="21"/>
-      <c r="H5" s="21">
+      <c r="G5" s="21" t="n"/>
+      <c r="H5" s="21" t="n">
         <v>100</v>
       </c>
-      <c r="I5" s="21">
+      <c r="I5" s="21" t="n">
         <v>30</v>
       </c>
-      <c r="J5" s="21">
+      <c r="J5" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="K5" s="21">
+      <c r="K5" s="21" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21">
+      <c r="A6" s="21" t="n">
         <v>50006</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">폭격 미사일</t>
+        <is>
+          <t>폭격 미사일</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">5초 동안 강력한 포격을 퍼붓습니다.</t>
-        </is>
-      </c>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="21"/>
-      <c r="J6" s="21"/>
-      <c r="K6" s="21">
+        <is>
+          <t>5초 동안 강력한 포격을 퍼붓습니다.</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="n"/>
+      <c r="E6" s="21" t="n"/>
+      <c r="H6" s="21" t="n"/>
+      <c r="I6" s="21" t="n"/>
+      <c r="J6" s="21" t="n"/>
+      <c r="K6" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="L6" s="21"/>
+      <c r="L6" s="21" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="21"/>
-      <c r="B7" s="21"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="21"/>
-      <c r="I7" s="21"/>
-      <c r="J7" s="21"/>
-      <c r="K7" s="21"/>
-      <c r="L7" s="21"/>
+      <c r="A7" s="21" t="n"/>
+      <c r="B7" s="21" t="n"/>
+      <c r="C7" s="21" t="n"/>
+      <c r="D7" s="21" t="n"/>
+      <c r="E7" s="21" t="n"/>
+      <c r="F7" s="21" t="n"/>
+      <c r="G7" s="21" t="n"/>
+      <c r="H7" s="21" t="n"/>
+      <c r="I7" s="21" t="n"/>
+      <c r="J7" s="21" t="n"/>
+      <c r="K7" s="21" t="n"/>
+      <c r="L7" s="21" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="21"/>
-      <c r="B8" s="21"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="H8" s="21"/>
-      <c r="I8" s="21"/>
-      <c r="J8" s="21"/>
-      <c r="K8" s="21"/>
+      <c r="A8" s="21" t="n"/>
+      <c r="B8" s="21" t="n"/>
+      <c r="C8" s="21" t="n"/>
+      <c r="D8" s="21" t="n"/>
+      <c r="E8" s="21" t="n"/>
+      <c r="H8" s="21" t="n"/>
+      <c r="I8" s="21" t="n"/>
+      <c r="J8" s="21" t="n"/>
+      <c r="K8" s="21" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="21"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="H9" s="21"/>
-      <c r="I9" s="21"/>
-      <c r="J9" s="21"/>
-      <c r="K9" s="21"/>
-      <c r="L9" s="21"/>
+      <c r="A9" s="21" t="n"/>
+      <c r="B9" s="21" t="n"/>
+      <c r="C9" s="21" t="n"/>
+      <c r="D9" s="21" t="n"/>
+      <c r="E9" s="21" t="n"/>
+      <c r="H9" s="21" t="n"/>
+      <c r="I9" s="21" t="n"/>
+      <c r="J9" s="21" t="n"/>
+      <c r="K9" s="21" t="n"/>
+      <c r="L9" s="21" t="n"/>
     </row>
   </sheetData>
-  <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
-  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
+  <pageMargins left="0.6997222304344179" right="0.6997222304344179" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName="Sheet2">
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
-    <col min="2" max="2" width="13.78515625" style="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.0703125" style="21" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9" style="21" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.2109375" style="21" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="70.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col width="13.78515625" bestFit="1" customWidth="1" style="21" min="2" max="2"/>
+    <col width="19.0703125" bestFit="1" customWidth="1" style="21" min="3" max="3"/>
+    <col width="9" bestFit="1" customWidth="1" style="21" min="4" max="4"/>
+    <col width="17.2109375" bestFit="1" customWidth="1" style="21" min="5" max="5"/>
+    <col width="70.5703125" bestFit="1" customWidth="1" style="21" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="inlineStr">
-        <v>id</v>
-        <is>
-          <t xml:space="preserve">id</t>
+        <is>
+          <t>id</t>
         </is>
       </c>
       <c r="B1" s="21" t="inlineStr">
-        <v>name</v>
-        <is>
-          <t xml:space="preserve">name</t>
+        <is>
+          <t>name</t>
         </is>
       </c>
       <c r="C1" s="21" t="inlineStr">
-        <v>passive_type</v>
-        <is>
-          <t xml:space="preserve">passive_type</t>
+        <is>
+          <t>passive_type</t>
         </is>
       </c>
       <c r="D1" s="21" t="inlineStr">
-        <v>param1</v>
-        <is>
-          <t xml:space="preserve">param1</t>
+        <is>
+          <t>param1</t>
         </is>
       </c>
       <c r="E1" s="21" t="inlineStr">
-        <v>param2</v>
-        <is>
-          <t xml:space="preserve">param2</t>
+        <is>
+          <t>param2</t>
         </is>
       </c>
       <c r="F1" s="21" t="inlineStr">
-        <v>param3</v>
-        <is>
-          <t xml:space="preserve">param3</t>
+        <is>
+          <t>param3</t>
         </is>
       </c>
       <c r="G1" s="21" t="inlineStr">
-        <v>description</v>
-        <is>
-          <t xml:space="preserve">description</t>
+        <is>
+          <t>description</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="21">
+      <c r="A2" s="21" t="n">
         <v>60001</v>
       </c>
       <c r="B2" s="21" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">폭발탄</t>
+        <is>
+          <t>폭발탄</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">OverrideEveryN</t>
+        <is>
+          <t>OverrideEveryN</t>
         </is>
       </c>
       <c r="D2" s="21" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">5</t>
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="E2" s="21" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">ExplosionProjectile</t>
-        </is>
-      </c>
-      <c r="F2" s="21"/>
+        <is>
+          <t>ExplosionProjectile</t>
+        </is>
+      </c>
+      <c r="F2" s="21" t="n"/>
       <c r="G2" s="5" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">5회 공격마다 폭발 투사체 발사.</t>
+        <is>
+          <t>5회 공격마다 폭발 투사체 발사.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11">
+      <c r="A3" s="11" t="n">
         <v>60002</v>
       </c>
       <c r="B3" s="10" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">범위 화염</t>
+        <is>
+          <t>범위 화염</t>
         </is>
       </c>
       <c r="C3" s="11" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">StatModifier</t>
+        <is>
+          <t>StatModifier</t>
         </is>
       </c>
       <c r="D3" s="11" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">AttackRange</t>
+        <is>
+          <t>AttackRange</t>
         </is>
       </c>
       <c r="E3" s="11" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">50</t>
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="F3" s="11" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">AttackArea:50</t>
+        <is>
+          <t>AttackArea:50</t>
         </is>
       </c>
       <c r="G3" s="10" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">사거리가 길어지고 범위가 넓어짐.</t>
+        <is>
+          <t>사거리가 길어지고 범위가 넓어짐.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11">
+      <c r="A4" s="11" t="n">
         <v>60003</v>
       </c>
       <c r="B4" s="10" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">활활 화염</t>
+        <is>
+          <t>활활 화염</t>
         </is>
       </c>
       <c r="C4" s="11" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">StatModifier</t>
+        <is>
+          <t>StatModifier</t>
         </is>
       </c>
       <c r="D4" s="11" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">AttackRange</t>
+        <is>
+          <t>AttackRange</t>
         </is>
       </c>
       <c r="E4" s="11" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">-30</t>
+        <is>
+          <t>-30</t>
         </is>
       </c>
       <c r="F4" s="11" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">AttackArea:-30:AttackDamage:150</t>
+        <is>
+          <t>AttackArea:-30:AttackDamage:150</t>
         </is>
       </c>
       <c r="G4" s="10" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">사거리와 범위가 좁아지지만 공격력이 크게 상승.</t>
+        <is>
+          <t>사거리와 범위가 좁아지지만 공격력이 크게 상승.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8">
+      <c r="A5" s="8" t="n">
         <v>60004</v>
       </c>
       <c r="B5" s="7" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">범위 냉기</t>
-        </is>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8">
-        <v>3</v>
-      </c>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8">
-        <v>1</v>
+        <is>
+          <t>범위 냉기</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>StatModifier</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>AttackRange</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>AttackDamage:30</t>
+        </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">범위가 넓어지고 공격력이 높아짐</t>
+        <is>
+          <t>범위가 넓어지고 공격력이 높아짐</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8">
+      <c r="A6" s="8" t="n">
         <v>60005</v>
       </c>
       <c r="B6" s="7" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">눈덩이</t>
+        <is>
+          <t>눈덩이</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">OverrideEveryN</t>
-        </is>
-      </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
+        <is>
+          <t>PeriodicSpawn</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>SnowballProjectile</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="G6" s="7" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">3초마다 적에게 범위 피해를 주고 1 초 동안 둔화 시키는 눈덩이를 발사</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" s="16" customFormat="1">
-      <c r="A7" s="16">
+        <is>
+          <t>3초마다 적에게 범위 피해를 주고 1 초 동안 둔화 시키는 눈덩이를 발사</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" customFormat="1" s="16">
+      <c r="A7" s="16" t="n">
         <v>60006</v>
       </c>
       <c r="B7" s="16" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">후폭발</t>
+        <is>
+          <t>후폭발</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">FollowUpExplosion</t>
+        <is>
+          <t>FollowUpExplosion</t>
         </is>
       </c>
       <c r="D7" s="16" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">0.2</t>
+        <is>
+          <t>0.2</t>
         </is>
       </c>
       <c r="E7" s="16" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">ExplosionProjectile</t>
+        <is>
+          <t>ExplosionProjectile</t>
         </is>
       </c>
       <c r="F7" s="16" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">3</t>
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="G7" s="16" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">공격 후 0.2초 뒤 반경 3의 폭발 생성</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" s="16" customFormat="1">
-      <c r="A8" s="16">
+        <is>
+          <t>공격 후 0.2초 뒤 반경 3의 폭발 생성</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" customFormat="1" s="16">
+      <c r="A8" s="16" t="n">
         <v>60007</v>
       </c>
       <c r="B8" s="17" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">강한 폭발</t>
+        <is>
+          <t>강한 폭발</t>
         </is>
       </c>
       <c r="G8" s="17" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">넉백이 없어지지만 공격력이 크게 상승합니다.</t>
+        <is>
+          <t>넉백이 없어지지만 공격력이 크게 상승합니다.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="22">
+      <c r="A9" s="22" t="n">
         <v>60008</v>
       </c>
       <c r="B9" s="19" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">부채 발사</t>
-        </is>
-      </c>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
+        <is>
+          <t>부채 발사</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="n"/>
+      <c r="D9" s="22" t="n"/>
+      <c r="E9" s="22" t="n"/>
+      <c r="F9" s="22" t="n"/>
       <c r="G9" s="19" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">부채꼴로 3 발 동시 발사</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" s="22" customFormat="1">
-      <c r="A10" s="22">
+        <is>
+          <t>부채꼴로 3 발 동시 발사</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" customFormat="1" s="22">
+      <c r="A10" s="22" t="n">
         <v>60009</v>
       </c>
       <c r="B10" s="19" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">빠른 미사일</t>
+        <is>
+          <t>빠른 미사일</t>
         </is>
       </c>
       <c r="G10" s="19" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">공격속도 증가 적 맞으면 약한 넉백</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" s="22" customFormat="1">
-      <c r="A11" s="22">
+        <is>
+          <t>공격속도 증가 적 맞으면 약한 넉백</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" customFormat="1" s="22">
+      <c r="A11" s="22" t="n">
         <v>60010</v>
       </c>
       <c r="B11" s="19" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">강화 미사일</t>
+        <is>
+          <t>강화 미사일</t>
         </is>
       </c>
       <c r="G11" s="19" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">공격력 증가, 범위 증가, 미사일 크기 증가</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" s="25" customFormat="1">
-      <c r="A12" s="25">
+        <is>
+          <t>공격력 증가, 범위 증가, 미사일 크기 증가</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" customFormat="1" s="25">
+      <c r="A12" s="25" t="n">
         <v>60011</v>
       </c>
       <c r="B12" s="24" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">연속 레이저</t>
+        <is>
+          <t>연속 레이저</t>
         </is>
       </c>
       <c r="G12" s="24" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">공격할 때 0.2초 딜레이로 3번 연속 공격</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" s="25" customFormat="1">
-      <c r="A13" s="25">
+        <is>
+          <t>공격할 때 0.2초 딜레이로 3번 연속 공격</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" customFormat="1" s="25">
+      <c r="A13" s="25" t="n">
         <v>60012</v>
       </c>
       <c r="B13" s="24" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">강한 레이저</t>
+        <is>
+          <t>강한 레이저</t>
         </is>
       </c>
       <c r="G13" s="24" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">범위 엄청 넓어지고 공격력 증가</t>
+        <is>
+          <t>범위 엄청 넓어지고 공격력 증가</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="21">
+      <c r="A14" s="21" t="n">
         <v>60013</v>
       </c>
       <c r="B14" s="5" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">더 빠른 전기</t>
-        </is>
-      </c>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
+        <is>
+          <t>더 빠른 전기</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="n"/>
+      <c r="D14" s="21" t="n"/>
+      <c r="E14" s="21" t="n"/>
+      <c r="F14" s="21" t="n"/>
       <c r="G14" s="5" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">공격 속도가 증가</t>
+        <is>
+          <t>공격 속도가 증가</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="21">
+      <c r="A15" s="21" t="n">
         <v>60014</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">범위 포격</t>
-        </is>
-      </c>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
+        <is>
+          <t>범위 포격</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="n"/>
+      <c r="D15" s="21" t="n"/>
+      <c r="E15" s="21" t="n"/>
+      <c r="F15" s="21" t="n"/>
       <c r="G15" s="5" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">포격 미사일의 범위 증가</t>
+        <is>
+          <t>포격 미사일의 범위 증가</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="21">
+      <c r="A16" s="21" t="n">
         <v>60015</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">폭격</t>
-        </is>
-      </c>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
+        <is>
+          <t>폭격</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="n"/>
+      <c r="D16" s="21" t="n"/>
+      <c r="E16" s="21" t="n"/>
+      <c r="F16" s="21" t="n"/>
       <c r="G16" s="5" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">공격 속도가 매우 빨라지지만 범위가 좁아지고 화면 내에서 무작위 위치에 폭격</t>
+        <is>
+          <t>공격 속도가 매우 빨라지지만 범위가 좁아지고 화면 내에서 무작위 위치에 폭격</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="21">
+      <c r="A17" s="21" t="n">
         <v>60016</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">관통 저격</t>
+        <is>
+          <t>관통 저격</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">총알이 적을 관통함.</t>
+        <is>
+          <t>총알이 적을 관통함.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="21">
+      <c r="A18" s="21" t="n">
         <v>60017</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">행운 저격</t>
+        <is>
+          <t>행운 저격</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">30%의 확률로 연속 공격</t>
+        <is>
+          <t>30%의 확률로 연속 공격</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="21">
+      <c r="A19" s="21" t="n">
         <v>60018</v>
       </c>
       <c r="B19" s="5" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">이게 저격?</t>
+        <is>
+          <t>이게 저격?</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">공격속도 증가</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" s="21" customFormat="1">
-      <c r="A20" s="21"/>
-      <c r="B20" s="21"/>
-      <c r="C20" s="21"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="21"/>
-    </row>
-    <row r="21" s="21" customFormat="1">
-      <c r="A21" s="21"/>
-      <c r="B21" s="21"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="5"/>
-    </row>
-    <row r="22" s="21" customFormat="1">
-      <c r="A22" s="21"/>
-      <c r="B22" s="21"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="21"/>
-      <c r="G22" s="5"/>
+        <is>
+          <t>공격속도 증가</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" customFormat="1" s="21">
+      <c r="A20" s="21" t="n"/>
+      <c r="B20" s="21" t="n"/>
+      <c r="C20" s="21" t="n"/>
+      <c r="D20" s="21" t="n"/>
+      <c r="E20" s="21" t="n"/>
+      <c r="F20" s="21" t="n"/>
+      <c r="G20" s="21" t="n"/>
+    </row>
+    <row r="21" customFormat="1" s="21">
+      <c r="A21" s="21" t="n"/>
+      <c r="B21" s="21" t="n"/>
+      <c r="C21" s="21" t="n"/>
+      <c r="D21" s="21" t="n"/>
+      <c r="E21" s="21" t="n"/>
+      <c r="F21" s="21" t="n"/>
+      <c r="G21" s="5" t="n"/>
+    </row>
+    <row r="22" customFormat="1" s="21">
+      <c r="A22" s="21" t="n"/>
+      <c r="B22" s="21" t="n"/>
+      <c r="C22" s="21" t="n"/>
+      <c r="D22" s="21" t="n"/>
+      <c r="E22" s="21" t="n"/>
+      <c r="F22" s="21" t="n"/>
+      <c r="G22" s="5" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="0"/>
 </worksheet>
 </file>
--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -1125,12 +1125,12 @@
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>AttackDamage:30</t>
+          <t>AttackArea:100:AttackDamage:30</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>범위가 넓어지고 공격력이 높아짐</t>
+          <t>사거리와 범위가 넓어지고 공격력이 높아짐</t>
         </is>
       </c>
     </row>

--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -1195,12 +1195,12 @@
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-1:0.5:0.3</t>
         </is>
       </c>
       <c r="G7" s="16" t="inlineStr">
         <is>
-          <t>공격 후 0.2초 뒤 반경 3의 폭발 생성</t>
+          <t>공격 후 0.2초 뒤 동일 범위의 약한 폭발 생성 (데미지 50%, 넉백 30%)</t>
         </is>
       </c>
     </row>

--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -892,15 +892,25 @@
           <t>5초 동안 강력한 포격을 퍼붓습니다.</t>
         </is>
       </c>
-      <c r="D6" s="21" t="n"/>
-      <c r="E6" s="21" t="n"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>SelfBuff</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="n">
+        <v>30</v>
+      </c>
       <c r="H6" s="21" t="n"/>
       <c r="I6" s="21" t="n"/>
       <c r="J6" s="21" t="n"/>
       <c r="K6" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="L6" s="21" t="n"/>
+      <c r="L6" s="21" t="inlineStr">
+        <is>
+          <t>AttackInterval:-80|AttackDamage:100</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="21" t="n"/>

--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -658,7 +658,7 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
     <col width="20.2109375" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -841,79 +841,106 @@
       </c>
     </row>
     <row r="5" customFormat="1" s="21">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" t="n">
+        <v>50005</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>전기 충격</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>하늘에서 번개가 떨어져 넓은 원형 범위에 피해를 준다.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AreaStrike</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>30</v>
+      </c>
+      <c r="H5" t="n">
+        <v>100</v>
+      </c>
+      <c r="I5" t="n">
+        <v>30</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>50005</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>전기 충격</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>하늘에서 번개가 떨어져 넓은 원형 범위에 피해를 준다.</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t>Projectile</t>
         </is>
       </c>
-      <c r="E5" s="21" t="n">
+      <c r="E6" s="21" t="n">
         <v>30</v>
       </c>
-      <c r="G5" s="21" t="n"/>
-      <c r="H5" s="21" t="n">
+      <c r="G6" s="21" t="n"/>
+      <c r="H6" s="21" t="n">
         <v>100</v>
       </c>
-      <c r="I5" s="21" t="n">
+      <c r="I6" s="21" t="n">
         <v>30</v>
       </c>
-      <c r="J5" s="21" t="n">
+      <c r="J6" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="K5" s="21" t="n">
+      <c r="K6" s="21" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="21" t="n">
+    <row r="7">
+      <c r="A7" s="21" t="n">
         <v>50006</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>폭격 미사일</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>5초 동안 강력한 포격을 퍼붓습니다.</t>
         </is>
       </c>
-      <c r="D6" s="21" t="n"/>
-      <c r="E6" s="21" t="n"/>
-      <c r="H6" s="21" t="n"/>
-      <c r="I6" s="21" t="n"/>
-      <c r="J6" s="21" t="n"/>
-      <c r="K6" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="L6" s="21" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="21" t="n"/>
-      <c r="B7" s="21" t="n"/>
-      <c r="C7" s="21" t="n"/>
-      <c r="D7" s="21" t="n"/>
-      <c r="E7" s="21" t="n"/>
-      <c r="F7" s="21" t="n"/>
-      <c r="G7" s="21" t="n"/>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>Bombard</t>
+        </is>
+      </c>
+      <c r="E7" s="21">
+        <v>30</v>
+      </c>
       <c r="H7" s="21" t="n"/>
       <c r="I7" s="21" t="n"/>
       <c r="J7" s="21" t="n"/>
-      <c r="K7" s="21" t="n"/>
+      <c r="K7" s="21" t="n">
+        <v>5</v>
+      </c>
       <c r="L7" s="21" t="n"/>
     </row>
     <row r="8">
@@ -922,10 +949,13 @@
       <c r="C8" s="21" t="n"/>
       <c r="D8" s="21" t="n"/>
       <c r="E8" s="21" t="n"/>
+      <c r="F8" s="21" t="n"/>
+      <c r="G8" s="21" t="n"/>
       <c r="H8" s="21" t="n"/>
       <c r="I8" s="21" t="n"/>
       <c r="J8" s="21" t="n"/>
       <c r="K8" s="21" t="n"/>
+      <c r="L8" s="21" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="21" t="n"/>
@@ -937,7 +967,18 @@
       <c r="I9" s="21" t="n"/>
       <c r="J9" s="21" t="n"/>
       <c r="K9" s="21" t="n"/>
-      <c r="L9" s="21" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="21" t="n"/>
+      <c r="B10" s="21" t="n"/>
+      <c r="C10" s="21" t="n"/>
+      <c r="D10" s="21" t="n"/>
+      <c r="E10" s="21" t="n"/>
+      <c r="H10" s="21" t="n"/>
+      <c r="I10" s="21" t="n"/>
+      <c r="J10" s="21" t="n"/>
+      <c r="K10" s="21" t="n"/>
+      <c r="L10" s="21" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.6997222304344179" right="0.6997222304344179" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
@@ -1277,6 +1318,21 @@
           <t>연속 레이저</t>
         </is>
       </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>RepeatAfterAttack</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="G12" s="24" t="inlineStr">
         <is>
           <t>공격할 때 0.2초 딜레이로 3번 연속 공격</t>
@@ -1292,6 +1348,26 @@
           <t>강한 레이저</t>
         </is>
       </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>StatModifier</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>AttackArea</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>AttackDamage:50</t>
+        </is>
+      </c>
       <c r="G13" s="24" t="inlineStr">
         <is>
           <t>범위 엄청 넓어지고 공격력 증가</t>
@@ -1307,13 +1383,25 @@
           <t>더 빠른 전기</t>
         </is>
       </c>
-      <c r="C14" s="21" t="n"/>
-      <c r="D14" s="21" t="n"/>
-      <c r="E14" s="21" t="n"/>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>StatModifier</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>AttackInterval</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>-20</t>
+        </is>
+      </c>
       <c r="F14" s="21" t="n"/>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>공격 속도가 증가</t>
+          <t>공격 속도 20% 증가</t>
         </is>
       </c>
     </row>
@@ -1326,9 +1414,21 @@
           <t>범위 포격</t>
         </is>
       </c>
-      <c r="C15" s="21" t="n"/>
-      <c r="D15" s="21" t="n"/>
-      <c r="E15" s="21" t="n"/>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>StatModifier</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>AttackArea</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
       <c r="F15" s="21" t="n"/>
       <c r="G15" s="5" t="inlineStr">
         <is>
@@ -1345,10 +1445,26 @@
           <t>폭격</t>
         </is>
       </c>
-      <c r="C16" s="21" t="n"/>
-      <c r="D16" s="21" t="n"/>
-      <c r="E16" s="21" t="n"/>
-      <c r="F16" s="21" t="n"/>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>RapidBombard</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>-50</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>-50</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>2:10:7</t>
+        </is>
+      </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
           <t>공격 속도가 매우 빨라지지만 범위가 좁아지고 화면 내에서 무작위 위치에 폭격</t>

--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -1,40 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600"/>
   </bookViews>
   <sheets>
-    <sheet name="active_skill_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="passive_skill_data" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="active_skill_data" sheetId="1" r:id="rId1"/>
+    <sheet name="passive_skill_data" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
   <fonts count="3">
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
       <charset val="129"/>
-      <family val="3"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="8"/>
       <name val="돋움"/>
+      <family val="3"/>
       <charset val="129"/>
-      <family val="3"/>
-      <sz val="8"/>
     </font>
   </fonts>
   <fills count="8">
@@ -96,80 +99,80 @@
     </xf>
   </cellStyleXfs>
   <cellXfs count="26">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -195,17 +198,17 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
       </font>
       <border>
         <top style="thin">
@@ -215,7 +218,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
       </font>
       <border>
         <bottom style="medium">
@@ -258,7 +261,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color rgb="FFFFFFFF"/>
       </font>
       <fill>
@@ -270,7 +273,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color rgb="FFFFFFFF"/>
       </font>
       <fill>
@@ -282,7 +285,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color rgb="FFFFFFFF"/>
       </font>
       <fill>
@@ -299,7 +302,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color rgb="FFFFFFFF"/>
       </font>
       <fill>
@@ -653,860 +656,1003 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet1">
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
-    <col width="20.2109375" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
-    <col width="12.28515625" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
-    <col width="49.78515625" bestFit="1" customWidth="1" style="3" min="3" max="3"/>
-    <col width="12.28515625" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
-    <col width="13.42578125" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
-    <col width="10.85546875" bestFit="1" customWidth="1" style="3" min="6" max="6"/>
-    <col width="22" bestFit="1" customWidth="1" style="3" min="7" max="7"/>
-    <col width="21" bestFit="1" customWidth="1" style="3" min="8" max="8"/>
-    <col width="18.85546875" bestFit="1" customWidth="1" style="3" min="9" max="9"/>
-    <col width="18.7109375" bestFit="1" customWidth="1" style="3" min="10" max="10"/>
-    <col width="16.28515625" customWidth="1" style="3" min="11" max="11"/>
-    <col width="17.42578125" bestFit="1" customWidth="1" style="3" min="12" max="12"/>
+    <col min="1" max="1" width="20.2109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.78515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.28515625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="17.42578125" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="inlineStr">
-        <is>
-          <t>id</t>
+        <v>id</v>
+        <is>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="B1" s="21" t="inlineStr">
-        <is>
-          <t>name</t>
+        <v>name</v>
+        <is>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C1" s="21" t="inlineStr">
-        <is>
-          <t>description</t>
+        <v>description</v>
+        <is>
+          <t xml:space="preserve">description</t>
         </is>
       </c>
       <c r="D1" s="21" t="inlineStr">
-        <is>
-          <t>skill_type</t>
+        <v>skill_type</v>
+        <is>
+          <t xml:space="preserve">skill_type</t>
         </is>
       </c>
       <c r="E1" s="21" t="inlineStr">
-        <is>
-          <t>skill_cooldown</t>
+        <v>skill_cooldown</v>
+        <is>
+          <t xml:space="preserve">skill_cooldown</t>
         </is>
       </c>
       <c r="F1" s="21" t="inlineStr">
-        <is>
-          <t>skill_icon_id</t>
+        <v>skill_icon_id</v>
+        <is>
+          <t xml:space="preserve">skill_icon_id</t>
         </is>
       </c>
       <c r="G1" s="21" t="inlineStr">
-        <is>
-          <t>skill_projectile_prefab_id</t>
+        <v>skill_projectile_prefab_id</v>
+        <is>
+          <t xml:space="preserve">skill_projectile_prefab_id</t>
         </is>
       </c>
       <c r="H1" s="21" t="inlineStr">
-        <is>
-          <t>skill_projectile_damage</t>
+        <v>skill_projectile_damage</v>
+        <is>
+          <t xml:space="preserve">skill_projectile_damage</t>
         </is>
       </c>
       <c r="I1" s="21" t="inlineStr">
-        <is>
-          <t>skill_projectile_range</t>
+        <v>skill_projectile_range</v>
+        <is>
+          <t xml:space="preserve">skill_projectile_range</t>
         </is>
       </c>
       <c r="J1" s="21" t="inlineStr">
-        <is>
-          <t>skill_projectile_count</t>
+        <v>skill_projectile_count</v>
+        <is>
+          <t xml:space="preserve">skill_projectile_count</t>
         </is>
       </c>
       <c r="K1" s="21" t="inlineStr">
-        <is>
-          <t>skill_buff_duration</t>
+        <v>skill_buff_duration</v>
+        <is>
+          <t xml:space="preserve">skill_buff_duration</t>
         </is>
       </c>
       <c r="L1" s="21" t="inlineStr">
-        <is>
-          <t>skill_buffs</t>
+        <v>skill_buffs</v>
+        <is>
+          <t xml:space="preserve">skill_buffs</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="21" t="n">
+      <c r="A2" s="21">
         <v>50001</v>
       </c>
       <c r="B2" s="21" t="inlineStr">
-        <is>
-          <t>속사 모드</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">속사 모드</t>
         </is>
       </c>
       <c r="C2" s="21" t="inlineStr">
-        <is>
-          <t>5초간 공격 간격 50% 감소</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">5초간 공격 간격 50% 감소</t>
         </is>
       </c>
       <c r="D2" s="21" t="inlineStr">
-        <is>
-          <t>SelfBuff</t>
-        </is>
-      </c>
-      <c r="E2" s="21" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">SelfBuff</t>
+        </is>
+      </c>
+      <c r="E2" s="21">
         <v>20</v>
       </c>
-      <c r="H2" s="21" t="n">
+      <c r="H2" s="21">
         <v>0</v>
       </c>
-      <c r="I2" s="21" t="n">
+      <c r="I2" s="21">
         <v>0</v>
       </c>
-      <c r="J2" s="21" t="n">
+      <c r="J2" s="21">
         <v>0</v>
       </c>
-      <c r="K2" s="21" t="n">
+      <c r="K2" s="21">
         <v>5</v>
       </c>
       <c r="L2" s="21" t="inlineStr">
-        <is>
-          <t>AttackInterval:-50</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" customFormat="1" s="11">
-      <c r="A3" s="14" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">AttackInterval:-50</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" s="11" customFormat="1">
+      <c r="A3" s="14">
         <v>50003</v>
       </c>
       <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>블리자드</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">블리자드</t>
         </is>
       </c>
       <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>15초 동안 범위가 맵을 덮을 정도로 넓어짐</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="n"/>
-      <c r="E3" s="13" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">15초 동안 범위가 맵을 덮을 정도로 넓어짐</t>
+        </is>
+      </c>
+      <c r="D3" s="14"/>
+      <c r="E3" s="13">
         <v>30</v>
       </c>
-      <c r="F3" s="14" t="n"/>
-      <c r="G3" s="14" t="n"/>
-      <c r="H3" s="14" t="n"/>
-      <c r="I3" s="14" t="n"/>
-      <c r="J3" s="14" t="n"/>
-      <c r="K3" s="14" t="n">
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14">
         <v>15</v>
       </c>
-      <c r="L3" s="14" t="n"/>
-    </row>
-    <row r="4" customFormat="1" s="14">
-      <c r="A4" s="21" t="n">
+      <c r="L3" s="14"/>
+    </row>
+    <row r="4" s="14" customFormat="1">
+      <c r="A4" s="21">
         <v>50004</v>
       </c>
       <c r="B4" s="21" t="inlineStr">
-        <is>
-          <t>즉발 폭발</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">즉발 폭발</t>
         </is>
       </c>
       <c r="C4" s="21" t="inlineStr">
-        <is>
-          <t>즉시 주변에 폭발을 일으킨다</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">즉시 주변에 폭발을 일으킨다</t>
         </is>
       </c>
       <c r="D4" s="21" t="inlineStr">
-        <is>
-          <t>InstantAttack</t>
-        </is>
-      </c>
-      <c r="E4" s="21" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">InstantAttack</t>
+        </is>
+      </c>
+      <c r="E4" s="21">
         <v>20</v>
       </c>
-      <c r="H4" s="21" t="n">
+      <c r="H4" s="21">
         <v>0</v>
       </c>
-      <c r="I4" s="21" t="n">
+      <c r="I4" s="21">
         <v>0</v>
       </c>
-      <c r="J4" s="21" t="n">
+      <c r="J4" s="21">
         <v>0</v>
       </c>
-      <c r="K4" s="21" t="n">
+      <c r="K4" s="21">
         <v>0</v>
       </c>
     </row>
-    <row r="5" customFormat="1" s="21">
-      <c r="A5" s="21" t="n">
+    <row r="5" s="21" customFormat="1">
+      <c r="A5" s="21">
         <v>50005</v>
       </c>
       <c r="B5" s="21" t="inlineStr">
-        <is>
-          <t>전기 충격</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">전기 충격</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
-        <is>
-          <t>하늘에서 번개가 떨어져 넓은 원형 범위에 피해를 준다.</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">하늘에서 번개가 떨어져 넓은 원형 범위에 피해를 준다.</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr">
-        <is>
-          <t>AreaStrike</t>
-        </is>
-      </c>
-      <c r="E5" s="21" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">AreaStrike</t>
+        </is>
+      </c>
+      <c r="E5" s="21">
         <v>30</v>
       </c>
-      <c r="H5" s="21" t="n">
+      <c r="H5" s="21">
         <v>100</v>
       </c>
-      <c r="I5" s="21" t="n">
+      <c r="I5" s="21">
         <v>30</v>
       </c>
-      <c r="J5" s="21" t="n">
+      <c r="J5" s="21">
         <v>1</v>
       </c>
-      <c r="K5" s="21" t="n">
+      <c r="K5" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="n">
+      <c r="A6" s="21">
         <v>50006</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>폭격 미사일</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">폭격 미사일</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>5초 동안 강력한 포격을 퍼붓습니다.</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">5초 동안 강력한 포격을 퍼붓습니다.</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t>Bombard</t>
-        </is>
-      </c>
-      <c r="E6" s="21" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">Bombard</t>
+        </is>
+      </c>
+      <c r="E6" s="21">
         <v>30</v>
       </c>
-      <c r="H6" s="21" t="n"/>
-      <c r="I6" s="21" t="n"/>
-      <c r="J6" s="21" t="n"/>
-      <c r="K6" s="21" t="n">
+      <c r="H6" s="21"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="21">
         <v>5</v>
       </c>
-      <c r="L6" s="21" t="n"/>
+      <c r="L6" s="21"/>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="n"/>
-      <c r="B7" s="21" t="n"/>
-      <c r="C7" s="21" t="n"/>
-      <c r="D7" s="21" t="n"/>
-      <c r="E7" s="21" t="n"/>
-      <c r="F7" s="21" t="n"/>
-      <c r="G7" s="21" t="n"/>
-      <c r="H7" s="21" t="n"/>
-      <c r="I7" s="21" t="n"/>
-      <c r="J7" s="21" t="n"/>
-      <c r="K7" s="21" t="n"/>
-      <c r="L7" s="21" t="n"/>
+      <c r="A7" s="21"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="21"/>
+      <c r="L7" s="21"/>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="n"/>
-      <c r="B8" s="21" t="n"/>
-      <c r="C8" s="21" t="n"/>
-      <c r="D8" s="21" t="n"/>
-      <c r="E8" s="21" t="n"/>
-      <c r="H8" s="21" t="n"/>
-      <c r="I8" s="21" t="n"/>
-      <c r="J8" s="21" t="n"/>
-      <c r="K8" s="21" t="n"/>
+      <c r="A8" s="21"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="21"/>
+      <c r="K8" s="21"/>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="n"/>
-      <c r="B9" s="21" t="n"/>
-      <c r="C9" s="21" t="n"/>
-      <c r="D9" s="21" t="n"/>
-      <c r="E9" s="21" t="n"/>
-      <c r="H9" s="21" t="n"/>
-      <c r="I9" s="21" t="n"/>
-      <c r="J9" s="21" t="n"/>
-      <c r="K9" s="21" t="n"/>
-      <c r="L9" s="21" t="n"/>
+      <c r="A9" s="21"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="21"/>
+      <c r="L9" s="21"/>
     </row>
   </sheetData>
-  <pageMargins left="0.6997222304344179" right="0.6997222304344179" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="0"/>
+  <pageMargins left="0.699722230434418" right="0.699722230434418" top="0.75" bottom="0.75" header="0.300000011920929" footer="0.300000011920929"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet2">
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="17.6"/>
   <cols>
-    <col width="13.78515625" bestFit="1" customWidth="1" style="21" min="2" max="2"/>
-    <col width="19.0703125" bestFit="1" customWidth="1" style="21" min="3" max="3"/>
-    <col width="9" bestFit="1" customWidth="1" style="21" min="4" max="4"/>
-    <col width="17.2109375" bestFit="1" customWidth="1" style="21" min="5" max="5"/>
-    <col width="70.5703125" bestFit="1" customWidth="1" style="21" min="7" max="7"/>
+    <col min="2" max="2" width="13.78515625" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.0703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9" style="21" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.2109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="70.5703125" style="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="inlineStr">
-        <is>
-          <t>id</t>
+        <v>id</v>
+        <is>
+          <t xml:space="preserve">id</t>
         </is>
       </c>
       <c r="B1" s="21" t="inlineStr">
-        <is>
-          <t>name</t>
+        <v>name</v>
+        <is>
+          <t xml:space="preserve">name</t>
         </is>
       </c>
       <c r="C1" s="21" t="inlineStr">
-        <is>
-          <t>passive_type</t>
+        <v>passive_type</v>
+        <is>
+          <t xml:space="preserve">passive_type</t>
         </is>
       </c>
       <c r="D1" s="21" t="inlineStr">
-        <is>
-          <t>param1</t>
+        <v>param1</v>
+        <is>
+          <t xml:space="preserve">param1</t>
         </is>
       </c>
       <c r="E1" s="21" t="inlineStr">
-        <is>
-          <t>param2</t>
+        <v>param2</v>
+        <is>
+          <t xml:space="preserve">param2</t>
         </is>
       </c>
       <c r="F1" s="21" t="inlineStr">
-        <is>
-          <t>param3</t>
+        <v>param3</v>
+        <is>
+          <t xml:space="preserve">param3</t>
         </is>
       </c>
       <c r="G1" s="21" t="inlineStr">
-        <is>
-          <t>description</t>
+        <v>description</v>
+        <is>
+          <t xml:space="preserve">description</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="21" t="n">
+      <c r="A2" s="21">
         <v>60001</v>
       </c>
       <c r="B2" s="21" t="inlineStr">
-        <is>
-          <t>폭발탄</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">폭발탄</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>OverrideEveryN</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">OverrideEveryN</t>
         </is>
       </c>
       <c r="D2" s="21" t="inlineStr">
-        <is>
-          <t>5</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="E2" s="21" t="inlineStr">
-        <is>
-          <t>ExplosionProjectile</t>
-        </is>
-      </c>
-      <c r="F2" s="21" t="n"/>
+        <v/>
+        <is>
+          <t xml:space="preserve">ExplosionProjectile</t>
+        </is>
+      </c>
+      <c r="F2" s="21"/>
       <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>5회 공격마다 폭발 투사체 발사.</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">5회 공격마다 폭발 투사체 발사.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="n">
+      <c r="A3" s="11">
         <v>60002</v>
       </c>
       <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>범위 화염</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">범위 화염</t>
         </is>
       </c>
       <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>StatModifier</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">StatModifier</t>
         </is>
       </c>
       <c r="D3" s="11" t="inlineStr">
-        <is>
-          <t>AttackRange</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">AttackRange</t>
         </is>
       </c>
       <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>50</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">50</t>
         </is>
       </c>
       <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>AttackArea:50</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">AttackArea:50</t>
         </is>
       </c>
       <c r="G3" s="10" t="inlineStr">
-        <is>
-          <t>사거리가 길어지고 범위가 넓어짐.</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">사거리가 길어지고 범위가 넓어짐.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="n">
+      <c r="A4" s="11">
         <v>60003</v>
       </c>
       <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>활활 화염</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">활활 화염</t>
         </is>
       </c>
       <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>StatModifier</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">StatModifier</t>
         </is>
       </c>
       <c r="D4" s="11" t="inlineStr">
-        <is>
-          <t>AttackRange</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">AttackRange</t>
         </is>
       </c>
       <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>-30</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">-30</t>
         </is>
       </c>
       <c r="F4" s="11" t="inlineStr">
-        <is>
-          <t>AttackArea:-30:AttackDamage:150</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">AttackArea:-30:AttackDamage:150</t>
         </is>
       </c>
       <c r="G4" s="10" t="inlineStr">
-        <is>
-          <t>사거리와 범위가 좁아지지만 공격력이 크게 상승.</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">사거리와 범위가 좁아지지만 공격력이 크게 상승.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="n">
+      <c r="A5" s="8">
         <v>60004</v>
       </c>
       <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>범위 냉기</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">범위 냉기</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>StatModifier</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">StatModifier</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>AttackRange</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">AttackRange</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>100</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">100</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>AttackArea:100:AttackDamage:30</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">AttackArea:100:AttackDamage:30</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>사거리와 범위가 넓어지고 공격력이 높아짐</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">사거리와 범위가 넓어지고 공격력이 높아짐</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="n">
+      <c r="A6" s="8">
         <v>60005</v>
       </c>
       <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>눈덩이</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">눈덩이</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>PeriodicSpawn</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">PeriodicSpawn</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>SnowballProjectile</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">SnowballProjectile</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>3초마다 적에게 범위 피해를 주고 1 초 동안 둔화 시키는 눈덩이를 발사</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" customFormat="1" s="16">
-      <c r="A7" s="16" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">3초마다 적에게 범위 피해를 주고 1 초 동안 둔화 시키는 눈덩이를 발사</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" s="16" customFormat="1">
+      <c r="A7" s="16">
         <v>60006</v>
       </c>
       <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>후폭발</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">후폭발</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>FollowUpExplosion</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">FollowUpExplosion</t>
         </is>
       </c>
       <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>0.2</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">0.2</t>
         </is>
       </c>
       <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>ExplosionProjectile</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">ExplosionProjectile</t>
         </is>
       </c>
       <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>-1:0.5:0.3</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">-1:0.5:0.3</t>
         </is>
       </c>
       <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>공격 후 0.2초 뒤 동일 범위의 약한 폭발 생성 (데미지 50%, 넉백 30%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" customFormat="1" s="16">
-      <c r="A8" s="16" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">공격 후 0.2초 뒤 동일 범위의 약한 폭발 생성 (데미지 50%, 넉백 30%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" s="16" customFormat="1">
+      <c r="A8" s="16">
         <v>60007</v>
       </c>
       <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>강한 폭발</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">강한 폭발</t>
         </is>
       </c>
       <c r="G8" s="17" t="inlineStr">
-        <is>
-          <t>넉백이 없어지지만 공격력이 크게 상승합니다.</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">넉백이 없어지지만 공격력이 크게 상승합니다.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="n">
+      <c r="A9" s="22">
         <v>60008</v>
       </c>
       <c r="B9" s="19" t="inlineStr">
-        <is>
-          <t>부채 발사</t>
-        </is>
-      </c>
-      <c r="C9" s="22" t="n"/>
-      <c r="D9" s="22" t="n"/>
-      <c r="E9" s="22" t="n"/>
-      <c r="F9" s="22" t="n"/>
+        <v/>
+        <is>
+          <t xml:space="preserve">부채 발사</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">StatModifier</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">AttackCount</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">200</t>
+        </is>
+      </c>
+      <c r="F9" s="22"/>
       <c r="G9" s="19" t="inlineStr">
-        <is>
-          <t>부채꼴로 3 발 동시 발사</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" customFormat="1" s="22">
-      <c r="A10" s="22" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">부채꼴로 3 발 동시 발사</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" s="22" customFormat="1">
+      <c r="A10" s="22">
         <v>60009</v>
       </c>
       <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>빠른 미사일</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">빠른 미사일</t>
         </is>
       </c>
       <c r="G10" s="19" t="inlineStr">
-        <is>
-          <t>공격속도 증가 적 맞으면 약한 넉백</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" customFormat="1" s="22">
-      <c r="A11" s="22" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">공격속도 증가 적 맞으면 약한 넉백</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" s="22" customFormat="1">
+      <c r="A11" s="22">
         <v>60010</v>
       </c>
       <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>강화 미사일</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">강화 미사일</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">StatModifier:AttackDamage:50:AttackArea:50|ScaleProjectile</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve">1.5</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <v/>
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="G11" s="19" t="inlineStr">
-        <is>
-          <t>공격력 증가, 범위 증가, 미사일 크기 증가</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" customFormat="1" s="25">
-      <c r="A12" s="25" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">공격력 증가, 범위 증가, 미사일 크기 증가</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" s="25" customFormat="1">
+      <c r="A12" s="25">
         <v>60011</v>
       </c>
       <c r="B12" s="24" t="inlineStr">
-        <is>
-          <t>연속 레이저</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">연속 레이저</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
-        <is>
-          <t>RepeatAfterAttack</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">RepeatAfterAttack</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
-        <is>
-          <t>0.2</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">0.2</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
-        <is>
-          <t>3</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="G12" s="24" t="inlineStr">
-        <is>
-          <t>공격할 때 0.2초 딜레이로 3번 연속 공격</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" customFormat="1" s="25">
-      <c r="A13" s="25" t="n">
+        <v/>
+        <is>
+          <t xml:space="preserve">공격할 때 0.2초 딜레이로 3번 연속 공격</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" s="25" customFormat="1">
+      <c r="A13" s="25">
         <v>60012</v>
       </c>
       <c r="B13" s="24" t="inlineStr">
-        <is>
-          <t>강한 레이저</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">강한 레이저</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
-        <is>
-          <t>StatModifier</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">StatModifier</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
-        <is>
-          <t>AttackArea</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">AttackArea</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
-        <is>
-          <t>100</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">100</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr">
-        <is>
-          <t>AttackDamage:50</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">AttackDamage:50</t>
         </is>
       </c>
       <c r="G13" s="24" t="inlineStr">
-        <is>
-          <t>범위 엄청 넓어지고 공격력 증가</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">범위 엄청 넓어지고 공격력 증가</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="21" t="n">
+      <c r="A14" s="21">
         <v>60013</v>
       </c>
       <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>더 빠른 전기</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">더 빠른 전기</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
-        <is>
-          <t>StatModifier</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">StatModifier</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t>AttackInterval</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">AttackInterval</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
-        <is>
-          <t>-30</t>
-        </is>
-      </c>
-      <c r="F14" s="21" t="n"/>
+        <v/>
+        <is>
+          <t xml:space="preserve">-30</t>
+        </is>
+      </c>
+      <c r="F14" s="21"/>
       <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>?? ?? 30% ??</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">?? ?? 30% ??</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="n">
+      <c r="A15" s="21">
         <v>60014</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>범위 포격</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">범위 포격</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
-        <is>
-          <t>StatModifier</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">StatModifier</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
-        <is>
-          <t>AttackArea</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">AttackArea</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="F15" s="21" t="n"/>
+        <v/>
+        <is>
+          <t xml:space="preserve">300</t>
+        </is>
+      </c>
+      <c r="F15" s="21"/>
       <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>포격 미사일의 범위 증가</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">포격 미사일의 범위 증가</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="21" t="n">
+      <c r="A16" s="21">
         <v>60015</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>폭격</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">폭격</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
-        <is>
-          <t>RapidBombard</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">RapidBombard</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t>-50</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">-50</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
-        <is>
-          <t>-50</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">-50</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr">
-        <is>
-          <t>2:10:7</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">2:10:7</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>공격 속도가 매우 빨라지지만 범위가 좁아지고 화면 내에서 무작위 위치에 폭격</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">공격 속도가 매우 빨라지지만 범위가 좁아지고 화면 내에서 무작위 위치에 폭격</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="21" t="n">
+      <c r="A17" s="21">
         <v>60016</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>관통 저격</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">관통 저격</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>총알이 적을 관통함.</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">총알이 적을 관통함.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="21" t="n">
+      <c r="A18" s="21">
         <v>60017</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>행운 저격</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">행운 저격</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>30%의 확률로 연속 공격</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">30%의 확률로 연속 공격</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="21" t="n">
+      <c r="A19" s="21">
         <v>60018</v>
       </c>
       <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>이게 저격?</t>
+        <v/>
+        <is>
+          <t xml:space="preserve">이게 저격?</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>공격속도 증가</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" customFormat="1" s="21">
-      <c r="A20" s="21" t="n"/>
-      <c r="B20" s="21" t="n"/>
-      <c r="C20" s="21" t="n"/>
-      <c r="D20" s="21" t="n"/>
-      <c r="E20" s="21" t="n"/>
-      <c r="F20" s="21" t="n"/>
-      <c r="G20" s="21" t="n"/>
-    </row>
-    <row r="21" customFormat="1" s="21">
-      <c r="A21" s="21" t="n"/>
-      <c r="B21" s="21" t="n"/>
-      <c r="C21" s="21" t="n"/>
-      <c r="D21" s="21" t="n"/>
-      <c r="E21" s="21" t="n"/>
-      <c r="F21" s="21" t="n"/>
-      <c r="G21" s="5" t="n"/>
-    </row>
-    <row r="22" customFormat="1" s="21">
-      <c r="A22" s="21" t="n"/>
-      <c r="B22" s="21" t="n"/>
-      <c r="C22" s="21" t="n"/>
-      <c r="D22" s="21" t="n"/>
-      <c r="E22" s="21" t="n"/>
-      <c r="F22" s="21" t="n"/>
-      <c r="G22" s="5" t="n"/>
+        <v/>
+        <is>
+          <t xml:space="preserve">공격속도 증가</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" s="21" customFormat="1">
+      <c r="A20" s="21"/>
+      <c r="B20" s="21"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
+    </row>
+    <row r="21" s="21" customFormat="1">
+      <c r="A21" s="21"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="5"/>
+    </row>
+    <row r="22" s="21" customFormat="1">
+      <c r="A22" s="21"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="0"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>
 </worksheet>
 </file>
--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="97">
   <si>
     <t xml:space="preserve">더 빠른 전기</t>
   </si>

--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -685,13 +685,13 @@
       <c r="B2" s="13" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">속사 모드</t>
+          <t xml:space="preserve">Skill_50001_Name</t>
         </is>
       </c>
       <c r="C2" s="13" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">5초간 공격 간격 50% 감소</t>
+          <t xml:space="preserve">Skill_50001_Desc</t>
         </is>
       </c>
       <c r="D2" s="13" t="inlineStr">
@@ -729,13 +729,13 @@
       <c r="B3" s="9" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">블리자드</t>
+          <t xml:space="preserve">Skill_50003_Name</t>
         </is>
       </c>
       <c r="C3" s="9" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">15초 동안 범위가 맵을 덮을 정도로 넓어짐</t>
+          <t xml:space="preserve">Skill_50003_Desc</t>
         </is>
       </c>
       <c r="D3" s="9"/>
@@ -759,13 +759,13 @@
       <c r="B4" s="13" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">즉발 폭발</t>
+          <t xml:space="preserve">Skill_50004_Name</t>
         </is>
       </c>
       <c r="C4" s="13" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">즉시 주변에 폭발을 일으킨다</t>
+          <t xml:space="preserve">Skill_50004_Desc</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
@@ -797,13 +797,13 @@
       <c r="B5" s="13" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">전기 충격</t>
+          <t xml:space="preserve">Skill_50005_Name</t>
         </is>
       </c>
       <c r="C5" s="13" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">하늘에서 번개가 떨어져 넓은 원형 범위에 피해를 준다.</t>
+          <t xml:space="preserve">Skill_50005_Desc</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
@@ -835,13 +835,13 @@
       <c r="B6" s="13" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">폭격 미사일</t>
+          <t xml:space="preserve">Skill_50006_Name</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">5초 동안 강력한 포격을 퍼붓습니다.</t>
+          <t xml:space="preserve">Skill_50006_Desc</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
@@ -971,7 +971,7 @@
       <c r="B2" s="13" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">폭발탄</t>
+          <t xml:space="preserve">Passive_60001_Name</t>
         </is>
       </c>
       <c r="C2" s="13" t="inlineStr">
@@ -996,7 +996,7 @@
       <c r="G2" s="13" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">5회 공격마다 폭발 투사체 발사.</t>
+          <t xml:space="preserve">Passive_60001_Desc</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       <c r="B3" s="7" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">범위 화염</t>
+          <t xml:space="preserve">Passive_60002_Name</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -1037,7 +1037,7 @@
       <c r="G3" s="7" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">사거리가 길어지고 범위가 넓어짐.</t>
+          <t xml:space="preserve">Passive_60002_Desc</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
       <c r="B4" s="7" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">활활 화염</t>
+          <t xml:space="preserve">Passive_60003_Name</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -1078,7 +1078,7 @@
       <c r="G4" s="7" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">사거리와 범위가 좁아지지만 공격력이 크게 상승.</t>
+          <t xml:space="preserve">Passive_60003_Desc</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1089,7 @@
       <c r="B5" s="5" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">범위 냉기</t>
+          <t xml:space="preserve">Passive_60004_Name</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -1119,7 +1119,7 @@
       <c r="G5" s="5" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">사거리와 범위가 넓어지고 공격력이 높아짐</t>
+          <t xml:space="preserve">Passive_60004_Desc</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
       <c r="B6" s="5" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">눈덩이</t>
+          <t xml:space="preserve">Passive_60005_Name</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -1160,7 +1160,7 @@
       <c r="G6" s="5" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">3초마다 적에게 범위 피해를 주고 1 초 동안 둔화 시키는 눈덩이를 발사</t>
+          <t xml:space="preserve">Passive_60005_Desc</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
       <c r="B7" s="11" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">후폭발</t>
+          <t xml:space="preserve">Passive_60006_Name</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -1201,7 +1201,7 @@
       <c r="G7" s="11" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">공격 후 0.2초 뒤 동일 범위의 약한 폭발 생성 (데미지 50%, 넉백 30%)</t>
+          <t xml:space="preserve">Passive_60006_Desc</t>
         </is>
       </c>
     </row>
@@ -1212,13 +1212,13 @@
       <c r="B8" s="11" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">강한 폭발</t>
+          <t xml:space="preserve">Passive_60007_Name</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">넉백이 없어지지만 공격력이 크게 상승합니다.</t>
+          <t xml:space="preserve">Passive_60007_Desc</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       <c r="B9" s="14" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">부채 발사</t>
+          <t xml:space="preserve">Passive_60008_Name</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
@@ -1254,7 +1254,7 @@
       <c r="G9" s="14" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">부채꼴로 3 발 동시 발사</t>
+          <t xml:space="preserve">Passive_60008_Desc</t>
         </is>
       </c>
     </row>
@@ -1265,13 +1265,13 @@
       <c r="B10" s="14" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">빠른 미사일</t>
+          <t xml:space="preserve">Passive_60009_Name</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">공격속도 증가 적 맞으면 약한 넉백</t>
+          <t xml:space="preserve">Passive_60009_Desc</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="B11" s="14" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">강화 미사일</t>
+          <t xml:space="preserve">Passive_60010_Name</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
@@ -1301,7 +1301,7 @@
       <c r="G11" s="14" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">공격력 증가, 범위 증가, 미사일 크기 증가</t>
+          <t xml:space="preserve">Passive_60010_Desc</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
       <c r="B12" s="16" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">연속 레이저</t>
+          <t xml:space="preserve">Passive_60011_Name</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr">
@@ -1336,7 +1336,7 @@
       <c r="G12" s="16" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">공격할 때 0.2초 딜레이로 3번 연속 공격</t>
+          <t xml:space="preserve">Passive_60011_Desc</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       <c r="B13" s="16" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">강한 레이저</t>
+          <t xml:space="preserve">Passive_60012_Name</t>
         </is>
       </c>
       <c r="C13" s="13" t="inlineStr">
@@ -1377,7 +1377,7 @@
       <c r="G13" s="16" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">범위 엄청 넓어지고 공격력 증가</t>
+          <t xml:space="preserve">Passive_60012_Desc</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       <c r="B14" s="13" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">더 빠른 전기</t>
+          <t xml:space="preserve">Passive_60013_Name</t>
         </is>
       </c>
       <c r="C14" s="13" t="inlineStr">
@@ -1413,7 +1413,7 @@
       <c r="G14" s="13" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">공격 속도가 증가</t>
+          <t xml:space="preserve">Passive_60013_Desc</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       <c r="B15" s="13" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">범위 포격</t>
+          <t xml:space="preserve">Passive_60014_Name</t>
         </is>
       </c>
       <c r="C15" s="13" t="inlineStr">
@@ -1449,7 +1449,7 @@
       <c r="G15" s="13" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">포격 미사일의 범위 증가</t>
+          <t xml:space="preserve">Passive_60014_Desc</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1460,7 @@
       <c r="B16" s="13" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">폭격</t>
+          <t xml:space="preserve">Passive_60015_Name</t>
         </is>
       </c>
       <c r="C16" s="13" t="inlineStr">
@@ -1490,7 +1490,7 @@
       <c r="G16" s="13" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">공격 속도가 매우 빨라지지만 범위가 좁아지고 화면 내에서 무작위 위치에 폭격</t>
+          <t xml:space="preserve">Passive_60015_Desc</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
       <c r="B17" s="13" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">관통 저격</t>
+          <t xml:space="preserve">Passive_60016_Name</t>
         </is>
       </c>
       <c r="C17" s="13" t="inlineStr">
@@ -1519,7 +1519,7 @@
       <c r="G17" s="13" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">총알이 적을 관통함.</t>
+          <t xml:space="preserve">Passive_60016_Desc</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       <c r="B18" s="13" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">행운 저격</t>
+          <t xml:space="preserve">Passive_60017_Name</t>
         </is>
       </c>
       <c r="C18" s="13" t="inlineStr">
@@ -1545,7 +1545,7 @@
           <t xml:space="preserve">30</t>
         </is>
       </c>
-      <c r="E18" s="0" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr">
         <v/>
         <is>
           <t xml:space="preserve">0.25</t>
@@ -1554,7 +1554,7 @@
       <c r="G18" s="13" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">30%의 확률로 연속 공격</t>
+          <t xml:space="preserve">Passive_60017_Desc</t>
         </is>
       </c>
     </row>
@@ -1565,7 +1565,7 @@
       <c r="B19" s="13" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">이게 저격?</t>
+          <t xml:space="preserve">Passive_60018_Name</t>
         </is>
       </c>
       <c r="C19" s="13" t="inlineStr">
@@ -1589,7 +1589,7 @@
       <c r="G19" s="13" t="inlineStr">
         <v/>
         <is>
-          <t xml:space="preserve">공격속도 증가</t>
+          <t xml:space="preserve">Passive_60018_Desc</t>
         </is>
       </c>
     </row>

--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="98">
   <si>
     <t xml:space="preserve">StatModifier:AttackDamage:50:AttackArea:50|ScaleProjectile</t>
   </si>

--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="98">
   <si>
     <t xml:space="preserve">StatModifier:AttackDamage:50:AttackArea:50|ScaleProjectile</t>
   </si>

--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="99">
   <si>
     <t xml:space="preserve">StatModifier:AttackDamage:50:AttackArea:50|ScaleProjectile</t>
   </si>
@@ -309,6 +309,9 @@
   </si>
   <si>
     <t xml:space="preserve">InstantAttack</t>
+  </si>
+  <si>
+    <t>MissileProjectile</t>
   </si>
 </sst>
 </file>
@@ -1076,7 +1079,7 @@
         <v>8</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="F2" s="6"/>
       <c r="G2" s="6" t="s">

--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="99">
   <si>
     <t xml:space="preserve">StatModifier:AttackDamage:50:AttackArea:50|ScaleProjectile</t>
   </si>
@@ -311,7 +311,7 @@
     <t xml:space="preserve">InstantAttack</t>
   </si>
   <si>
-    <t>MissileProjectile</t>
+    <t xml:space="preserve">MissileProjectile</t>
   </si>
 </sst>
 </file>

--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="99">
   <si>
     <t xml:space="preserve">StatModifier:AttackDamage:50:AttackArea:50|ScaleProjectile</t>
   </si>

--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="99">
   <si>
     <t xml:space="preserve">StatModifier:AttackDamage:50:AttackArea:50|ScaleProjectile</t>
   </si>

--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -1272,10 +1272,8 @@
           <t>AttackInterval</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>-30</t>
-        </is>
+      <c r="E14" s="6" t="n">
+        <v>-20</v>
       </c>
       <c r="F14" s="6" t="n"/>
       <c r="G14" s="6" t="inlineStr">

--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="100">
   <si>
     <t xml:space="preserve">StatModifier:AttackDamage:50:AttackArea:50|ScaleProjectile</t>
   </si>
@@ -312,6 +312,9 @@
   </si>
   <si>
     <t xml:space="preserve">skill_projectile_count</t>
+  </si>
+  <si>
+    <t>3:10</t>
   </si>
 </sst>
 </file>
@@ -1288,7 +1291,7 @@
         <v>35</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>8</v>
+        <v>99</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>43</v>

--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="103">
   <si>
     <t xml:space="preserve">StatModifier:AttackDamage:50:AttackArea:50|ScaleProjectile</t>
   </si>
@@ -315,6 +315,15 @@
   </si>
   <si>
     <t>3:10</t>
+  </si>
+  <si>
+    <t>AttackDamage</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>SlowRate:50</t>
   </si>
 </sst>
 </file>
@@ -1262,13 +1271,13 @@
         <v>90</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>41</v>

--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="112">
   <si>
     <t xml:space="preserve">StatModifier:AttackDamage:50:AttackArea:50|ScaleProjectile</t>
   </si>
@@ -324,6 +324,33 @@
   </si>
   <si>
     <t>SlowRate:50</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>AttackArea:100</t>
+  </si>
+  <si>
+    <t>-50</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>AttackDamage:100</t>
+  </si>
+  <si>
+    <t>AttackArea:50</t>
+  </si>
+  <si>
+    <t>-30</t>
+  </si>
+  <si>
+    <t>StatModifier:AttackDamage:100:AttackArea:50|ScaleProjectile</t>
   </si>
 </sst>
 </file>
@@ -1075,7 +1102,7 @@
         <v>27</v>
       </c>
       <c r="E5" s="6">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="H5" s="6">
         <v>100</v>
@@ -1104,7 +1131,7 @@
         <v>66</v>
       </c>
       <c r="E6" s="6">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H6" s="6"/>
       <c r="I6" s="6"/>
@@ -1228,10 +1255,10 @@
         <v>20</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>9</v>
+        <v>107</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>34</v>
@@ -1251,10 +1278,10 @@
         <v>23</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>7</v>
+        <v>110</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>67</v>
+        <v>108</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>46</v>
@@ -1354,7 +1381,7 @@
         <v>22</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>16</v>
+        <v>103</v>
       </c>
       <c r="F9" s="7"/>
       <c r="G9" s="7" t="s">
@@ -1380,7 +1407,7 @@
         <v>31</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>13</v>
@@ -1463,8 +1490,8 @@
       <c r="D15" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E15" s="6" t="s">
-        <v>12</v>
+      <c r="E15" s="6">
+        <v>150</v>
       </c>
       <c r="F15" s="6"/>
       <c r="G15" s="6" t="s">
@@ -1481,11 +1508,11 @@
       <c r="C16" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>17</v>
+      <c r="D16" s="6">
+        <v>-150</v>
+      </c>
+      <c r="E16" s="6">
+        <v>0</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>30</v>

--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="113">
   <si>
     <t xml:space="preserve">StatModifier:AttackDamage:50:AttackArea:50|ScaleProjectile</t>
   </si>
@@ -351,6 +351,9 @@
   </si>
   <si>
     <t>StatModifier:AttackDamage:100:AttackArea:50|ScaleProjectile</t>
+  </si>
+  <si>
+    <t>RepeatAfterAttack:0.15:1:1</t>
   </si>
 </sst>
 </file>
@@ -1375,14 +1378,10 @@
         <v>48</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>103</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7" t="s">
         <v>49</v>

--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="114">
   <si>
     <t xml:space="preserve">StatModifier:AttackDamage:50:AttackArea:50|ScaleProjectile</t>
   </si>
@@ -350,10 +350,13 @@
     <t>-30</t>
   </si>
   <si>
-    <t>StatModifier:AttackDamage:100:AttackArea:50|ScaleProjectile</t>
+    <t>StatModifier:AttackDamage:100|ScaleProjectile</t>
   </si>
   <si>
     <t>RepeatAfterAttack:0.15:1:1</t>
+  </si>
+  <si>
+    <t>StatModifier:AttackInterval:30|KnockbackOnHit:2:0.3</t>
   </si>
 </sst>
 </file>
@@ -1394,6 +1397,9 @@
       <c r="B10" s="7" t="s">
         <v>37</v>
       </c>
+      <c r="C10" s="7" t="s">
+        <v>113</v>
+      </c>
       <c r="G10" s="7" t="s">
         <v>50</v>
       </c>

--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -10,353 +10,307 @@
     <sheet name="active_skill_data" sheetId="1" r:id="rId4"/>
     <sheet name="passive_skill_data" sheetId="2" r:id="rId5"/>
   </sheets>
-  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="114">
-  <si>
-    <t xml:space="preserve">StatModifier:AttackDamage:50:AttackArea:50|ScaleProjectile</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="99">
+  <si>
+    <t xml:space="preserve">2:10:7</t>
   </si>
   <si>
     <t xml:space="preserve">0.25</t>
   </si>
   <si>
-    <t xml:space="preserve">AttackArea:100:AttackDamage:30</t>
+    <t xml:space="preserve">Bombard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">param2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">param3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">name</t>
   </si>
   <si>
     <t xml:space="preserve">param1</t>
   </si>
   <si>
-    <t xml:space="preserve">param2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">param3</t>
+    <t xml:space="preserve">3:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackDamage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackInterval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">passive_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OverrideEveryN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skill_icon_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackArea:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackDamage:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StatModifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RapidBombard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InstantAttack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PeriodicSpawn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skill_cooldown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skill_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackRange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skill_buffs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackArea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1:0.5:0.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AreaStrike</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SelfBuff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SlowRate:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-30</t>
   </si>
   <si>
     <t xml:space="preserve">id</t>
   </si>
   <si>
-    <t xml:space="preserve">-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
+    <t xml:space="preserve">0.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
   </si>
   <si>
     <t xml:space="preserve">50</t>
   </si>
   <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">300</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackRange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1:0.5:0.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackCount</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackArea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skill_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SelfBuff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skill_buffs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AreaStrike</t>
+    <t xml:space="preserve">Passive_60013_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill_50006_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill_50005_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60003_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60004_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60009_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill_50003_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60004_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill_50006_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill_50003_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60006_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SnowballProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60007_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60006_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60010_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60008_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60003_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60005_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackInterval:-50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60007_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60009_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FollowUpExplosion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60008_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60011_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackDamage:100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60005_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill_50005_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60018_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60014_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60013_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60017_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60015_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60012_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60017_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60014_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60011_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChainAttackChance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60012_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60018_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60015_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill_50001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skill_buff_duration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill_50001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60010_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill_50004_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill_50004_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StatModifier:AttackDamage:100|ScaleProjectile</t>
   </si>
   <si>
     <t xml:space="preserve">RepeatAfterAttack:0.2:3|StatModifier:AttackInterval:40</t>
   </si>
   <si>
-    <t xml:space="preserve">name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2:10:7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60010_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FollowUpExplosion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60003_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60002_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SnowballProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60004_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60009_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60006_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60007_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60004_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60005_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60005_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60006_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60003_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60007_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60008_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60008_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60009_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60011_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60014_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60013_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60011_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60014_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60012_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60018_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60017_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60017_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60012_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60018_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60013_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60015_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60015_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ChainAttackChance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bombard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackDamage:150</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60010_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill_50004_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill_50004_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill_50001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill_50003_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill_50005_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill_50006_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill_50005_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skill_buff_duration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill_50006_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill_50003_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill_50001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackInterval:-50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackDamage:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackInterval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RapidBombard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skill_cooldown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skill_icon_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InstantAttack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">StatModifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">passive_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OverrideEveryN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackArea:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PeriodicSpawn</t>
+    <t xml:space="preserve">StatModifier:AttackInterval:30|KnockbackOnHit:2:0.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RepeatAfterAttack:0.15:1:1</t>
   </si>
   <si>
     <t xml:space="preserve">skill_projectile_prefab_id</t>
   </si>
   <si>
+    <t xml:space="preserve">skill_projectile_count</t>
+  </si>
+  <si>
     <t xml:space="preserve">skill_projectile_range</t>
   </si>
   <si>
     <t xml:space="preserve">skill_projectile_damage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skill_projectile_count</t>
-  </si>
-  <si>
-    <t>3:10</t>
-  </si>
-  <si>
-    <t>AttackDamage</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>SlowRate:50</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>AttackArea:100</t>
-  </si>
-  <si>
-    <t>-50</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>AttackDamage:100</t>
-  </si>
-  <si>
-    <t>AttackArea:50</t>
-  </si>
-  <si>
-    <t>-30</t>
-  </si>
-  <si>
-    <t>StatModifier:AttackDamage:100|ScaleProjectile</t>
-  </si>
-  <si>
-    <t>RepeatAfterAttack:0.15:1:1</t>
-  </si>
-  <si>
-    <t>StatModifier:AttackInterval:30|KnockbackOnHit:2:0.3</t>
   </si>
 </sst>
 </file>
@@ -537,31 +491,7 @@
   <cellStyles count="1">
     <cellStyle xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFAEBFEA"/>
-          <bgColor rgb="FFAEBFEA"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF94A5DF"/>
-          <bgColor rgb="FF94A5DF"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color rgb="FF6182D6"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF6182D6"/>
-        </bottom>
-      </border>
-    </dxf>
+  <dxfs count="16">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -644,27 +574,104 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color rgb="FFBFBFBF"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFBFBFBF"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD9D9D9"/>
+          <bgColor rgb="FFD9D9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDCE6F2"/>
+          <bgColor rgb="FFDCE6F2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF96B3D7"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDCE6F2"/>
+          <bgColor rgb="FFDCE6F2"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color rgb="FF96B3D7"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB8CCE5"/>
+          <bgColor rgb="FFB8CCE5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB8CCE5"/>
+          <bgColor rgb="FFB8CCE5"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="8">
-      <tableStyleElement type="headerRow" size="1" dxfId="4"/>
-      <tableStyleElement type="totalRow" size="1" dxfId="3"/>
-      <tableStyleElement type="firstColumn" size="1" dxfId="2"/>
-      <tableStyleElement type="lastColumn" size="1" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" size="1" dxfId="1"/>
-      <tableStyleElement type="secondRowStripe" size="1"/>
-      <tableStyleElement type="firstColumnStripe" size="1" dxfId="1"/>
-      <tableStyleElement type="secondColumnStripe" size="1"/>
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="4">
+      <tableStyleElement type="headerRow" size="1" dxfId="2"/>
+      <tableStyleElement type="totalRow" size="1" dxfId="1"/>
+      <tableStyleElement type="firstColumn" size="1"/>
+      <tableStyleElement type="lastColumn" size="1"/>
     </tableStyle>
-    <tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="8">
-      <tableStyleElement type="wholeTable" size="1" dxfId="5"/>
-      <tableStyleElement type="headerRow" size="1" dxfId="10"/>
-      <tableStyleElement type="totalRow" size="1" dxfId="9"/>
-      <tableStyleElement type="firstColumn" size="1" dxfId="8"/>
-      <tableStyleElement type="lastColumn" size="1" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" size="1" dxfId="6"/>
-      <tableStyleElement type="secondRowStripe" size="1"/>
-      <tableStyleElement type="firstColumnStripe" size="1" dxfId="7"/>
+    <tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="7">
+      <tableStyleElement type="wholeTable" size="1" dxfId="3"/>
+      <tableStyleElement type="headerRow" size="1" dxfId="8"/>
+      <tableStyleElement type="totalRow" size="1" dxfId="7"/>
+      <tableStyleElement type="firstColumn" size="1" dxfId="6"/>
+      <tableStyleElement type="lastColumn" size="1" dxfId="6"/>
+      <tableStyleElement type="firstRowStripe" size="1" dxfId="4"/>
+      <tableStyleElement type="firstColumnStripe" size="1" dxfId="5"/>
     </tableStyle>
   </tableStyles>
 </styleSheet>
@@ -973,40 +980,40 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="6" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="C1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>87</v>
-      </c>
       <c r="F1" s="6" t="s">
-        <v>88</v>
+        <v>12</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>95</v>
       </c>
       <c r="H1" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="J1" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="J1" s="6" t="s">
-        <v>98</v>
-      </c>
       <c r="K1" s="6" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -1014,13 +1021,13 @@
         <v>50001</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E2" s="6">
         <v>20</v>
@@ -1038,7 +1045,7 @@
         <v>5</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:12" s="3" customFormat="1">
@@ -1046,37 +1053,40 @@
         <v>50003</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4">
-        <v>30</v>
-      </c>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4">
-        <v>15</v>
-      </c>
-      <c r="L3" s="4"/>
+        <v>45</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SelfBuff</t>
+        </is>
+      </c>
+      <c r="E3">
+        <v>20</v>
+      </c>
+      <c r="K3">
+        <v>10</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>AttackArea:250</t>
+        </is>
+      </c>
     </row>
     <row r="4" spans="1:11" s="4" customFormat="1">
       <c r="A4" s="6">
         <v>50004</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>89</v>
+        <v>17</v>
       </c>
       <c r="E4" s="6">
         <v>20</v>
@@ -1099,13 +1109,13 @@
         <v>50005</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>76</v>
+        <v>41</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E5" s="6">
         <v>10</v>
@@ -1128,13 +1138,13 @@
         <v>50006</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>66</v>
+        <v>2</v>
       </c>
       <c r="E6" s="6">
         <v>15</v>
@@ -1205,25 +1215,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
-        <v>5</v>
-      </c>
       <c r="G1" s="6" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -1231,20 +1241,20 @@
         <v>60001</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>92</v>
+        <v>11</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="F2" s="6"/>
       <c r="G2" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1252,22 +1262,22 @@
         <v>60002</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>107</v>
+        <v>38</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>109</v>
+        <v>13</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1275,22 +1285,22 @@
         <v>60003</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>110</v>
+        <v>34</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>108</v>
+        <v>66</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1298,22 +1308,22 @@
         <v>60004</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>101</v>
+        <v>38</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>102</v>
+        <v>28</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1321,22 +1331,22 @@
         <v>60005</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>94</v>
+        <v>18</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>99</v>
+        <v>7</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="5" customFormat="1">
@@ -1344,22 +1354,22 @@
         <v>60006</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="5" customFormat="1">
@@ -1367,10 +1377,15 @@
         <v>60007</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>47</v>
+        <v>53</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Strengthen:100|StatModifier:AttackArea:50</t>
+        </is>
       </c>
       <c r="G8" s="5" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1378,16 +1393,16 @@
         <v>60008</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="7" customFormat="1">
@@ -1395,13 +1410,13 @@
         <v>60009</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:7" s="7" customFormat="1">
@@ -1409,17 +1424,17 @@
         <v>60010</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E11" s="6"/>
       <c r="G11" s="7" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="8" customFormat="1">
@@ -1427,15 +1442,15 @@
         <v>60011</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>28</v>
+        <v>92</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
       <c r="G12" s="8" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:7" s="8" customFormat="1">
@@ -1443,22 +1458,22 @@
         <v>60012</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>84</v>
+        <v>14</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1466,20 +1481,20 @@
         <v>60013</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>85</v>
+        <v>9</v>
       </c>
       <c r="E14" s="6">
         <v>-20</v>
       </c>
       <c r="F14" s="6"/>
       <c r="G14" s="6" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1487,20 +1502,20 @@
         <v>60014</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E15" s="6">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F15" s="6"/>
       <c r="G15" s="6" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1508,22 +1523,22 @@
         <v>60015</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>86</v>
+        <v>16</v>
       </c>
       <c r="D16" s="6">
-        <v>-150</v>
+        <v>-50</v>
       </c>
       <c r="E16" s="6">
         <v>0</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:1">
@@ -1534,19 +1549,19 @@
         <v>60017</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>1</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1554,19 +1569,19 @@
         <v>60018</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>85</v>
+        <v>9</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" s="6" customFormat="1"/>

--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="99">
   <si>
     <t xml:space="preserve">2:10:7</t>
   </si>
@@ -1058,20 +1058,22 @@
       <c r="C3" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="0" t="inlineStr">
+        <v/>
         <is>
-          <t>SelfBuff</t>
+          <t xml:space="preserve">SelfBuff</t>
         </is>
       </c>
-      <c r="E3">
+      <c r="E3" s="0">
         <v>20</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="0">
         <v>10</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="0" t="inlineStr">
+        <v/>
         <is>
-          <t>AttackArea:250</t>
+          <t xml:space="preserve">AttackArea:250</t>
         </is>
       </c>
     </row>
@@ -1379,9 +1381,10 @@
       <c r="B8" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="0" t="inlineStr">
+        <v/>
         <is>
-          <t>Strengthen:100|StatModifier:AttackArea:50</t>
+          <t xml:space="preserve">Strengthen:100|StatModifier:AttackArea:50</t>
         </is>
       </c>
       <c r="G8" s="5" t="s">

--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -14,303 +14,306 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="100">
+  <si>
+    <t xml:space="preserve">30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bombard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">param2</t>
+  </si>
   <si>
     <t xml:space="preserve">2:10:7</t>
   </si>
   <si>
-    <t xml:space="preserve">0.25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bombard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">param2</t>
+    <t xml:space="preserve">param1</t>
   </si>
   <si>
     <t xml:space="preserve">param3</t>
   </si>
   <si>
-    <t xml:space="preserve">name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">param1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3:10</t>
+    <t xml:space="preserve">Passive_60006_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60002_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60006_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackInterval:-50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60003_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60008_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60007_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SnowballProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60005_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60004_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill_50006_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill_50003_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60009_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60003_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60014_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FollowUpExplosion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackDamage:100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill_50005_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill_50003_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60012_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60010_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60017_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60009_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60002_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill_50005_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60015_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60005_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60011_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60011_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60018_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill_50001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60013_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60010_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60007_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60008_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60015_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill_50004_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60001_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skill_buff_duration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60018_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExplosionProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60004_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MissileProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60012_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60017_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60014_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill_50006_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill_50001_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChainAttackChance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill_50004_Desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60013_Name</t>
   </si>
   <si>
     <t xml:space="preserve">AttackDamage</t>
   </si>
   <si>
+    <t xml:space="preserve">AttackDamage:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OverrideEveryN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RapidBombard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skill_cooldown</t>
+  </si>
+  <si>
     <t xml:space="preserve">AttackInterval</t>
   </si>
   <si>
     <t xml:space="preserve">passive_type</t>
   </si>
   <si>
-    <t xml:space="preserve">OverrideEveryN</t>
+    <t xml:space="preserve">PeriodicSpawn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InstantAttack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackArea:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackArea:250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StatModifier</t>
   </si>
   <si>
     <t xml:space="preserve">skill_icon_id</t>
   </si>
   <si>
-    <t xml:space="preserve">AttackArea:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackDamage:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">StatModifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RapidBombard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InstantAttack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PeriodicSpawn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skill_cooldown</t>
+    <t xml:space="preserve">StatModifier:AttackDamage:100|ScaleProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RepeatAfterAttack:0.2:3|StatModifier:AttackInterval:40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strengthen:100|StatModifier:AttackArea:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StatModifier:AttackInterval:30|KnockbackOnHit:2:0.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skill_buffs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SlowRate:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackRange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AttackArea</t>
   </si>
   <si>
     <t xml:space="preserve">skill_type</t>
   </si>
   <si>
-    <t xml:space="preserve">AttackRange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skill_buffs</t>
+    <t xml:space="preserve">SelfBuff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1:0.5:0.3</t>
   </si>
   <si>
     <t xml:space="preserve">description</t>
   </si>
   <si>
-    <t xml:space="preserve">AttackArea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1:0.5:0.3</t>
-  </si>
-  <si>
     <t xml:space="preserve">AreaStrike</t>
   </si>
   <si>
-    <t xml:space="preserve">SelfBuff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SlowRate:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60013_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill_50006_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill_50005_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60003_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60004_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60009_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill_50003_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60002_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60004_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill_50006_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill_50003_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60006_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExplosionProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SnowballProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60007_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60006_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60010_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60002_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60008_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60003_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60005_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackInterval:-50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60007_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60009_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FollowUpExplosion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60008_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60011_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AttackDamage:100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60005_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill_50005_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60018_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60014_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60013_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60017_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60015_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60012_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60017_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60014_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60011_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ChainAttackChance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60012_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60018_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60015_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill_50001_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skill_buff_duration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill_50001_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passive_60010_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MissileProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill_50004_Desc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill_50004_Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">StatModifier:AttackDamage:100|ScaleProjectile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RepeatAfterAttack:0.2:3|StatModifier:AttackInterval:40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">StatModifier:AttackInterval:30|KnockbackOnHit:2:0.3</t>
+    <t xml:space="preserve">skill_projectile_damage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skill_projectile_count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skill_projectile_range</t>
   </si>
   <si>
     <t xml:space="preserve">RepeatAfterAttack:0.15:1:1</t>
   </si>
   <si>
     <t xml:space="preserve">skill_projectile_prefab_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skill_projectile_count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skill_projectile_range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skill_projectile_damage</t>
   </si>
 </sst>
 </file>
@@ -491,23 +494,7 @@
   <cellStyles count="1">
     <cellStyle xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF6182D6"/>
-          <bgColor rgb="FF6182D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD9D9D9"/>
-          <bgColor rgb="FFD9D9D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="14">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -658,20 +645,17 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="4">
-      <tableStyleElement type="headerRow" size="1" dxfId="2"/>
-      <tableStyleElement type="totalRow" size="1" dxfId="1"/>
-      <tableStyleElement type="firstColumn" size="1"/>
-      <tableStyleElement type="lastColumn" size="1"/>
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="1">
+      <tableStyleElement type="headerRow" size="1"/>
     </tableStyle>
     <tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="7">
-      <tableStyleElement type="wholeTable" size="1" dxfId="3"/>
-      <tableStyleElement type="headerRow" size="1" dxfId="8"/>
-      <tableStyleElement type="totalRow" size="1" dxfId="7"/>
-      <tableStyleElement type="firstColumn" size="1" dxfId="6"/>
-      <tableStyleElement type="lastColumn" size="1" dxfId="6"/>
-      <tableStyleElement type="firstRowStripe" size="1" dxfId="4"/>
-      <tableStyleElement type="firstColumnStripe" size="1" dxfId="5"/>
+      <tableStyleElement type="wholeTable" size="1" dxfId="1"/>
+      <tableStyleElement type="headerRow" size="1" dxfId="6"/>
+      <tableStyleElement type="totalRow" size="1" dxfId="5"/>
+      <tableStyleElement type="firstColumn" size="1" dxfId="4"/>
+      <tableStyleElement type="lastColumn" size="1" dxfId="4"/>
+      <tableStyleElement type="firstRowStripe" size="1" dxfId="2"/>
+      <tableStyleElement type="firstColumnStripe" size="1" dxfId="3"/>
     </tableStyle>
   </tableStyles>
 </styleSheet>
@@ -980,28 +964,28 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="6" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>23</v>
+        <v>93</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>19</v>
+        <v>73</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="G1" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="H1" s="6" t="s">
         <v>95</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>98</v>
       </c>
       <c r="I1" s="6" t="s">
         <v>97</v>
@@ -1010,10 +994,10 @@
         <v>96</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>22</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -1021,13 +1005,13 @@
         <v>50001</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>27</v>
+        <v>91</v>
       </c>
       <c r="E2" s="6">
         <v>20</v>
@@ -1045,7 +1029,7 @@
         <v>5</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:12" s="3" customFormat="1">
@@ -1053,16 +1037,13 @@
         <v>50003</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D3" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">SelfBuff</t>
-        </is>
+        <v>36</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>91</v>
       </c>
       <c r="E3" s="0">
         <v>20</v>
@@ -1070,11 +1051,8 @@
       <c r="K3" s="0">
         <v>10</v>
       </c>
-      <c r="L3" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">AttackArea:250</t>
-        </is>
+      <c r="L3" s="0" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="4" customFormat="1">
@@ -1082,13 +1060,13 @@
         <v>50004</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>90</v>
+        <v>54</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>17</v>
+        <v>77</v>
       </c>
       <c r="E4" s="6">
         <v>20</v>
@@ -1111,13 +1089,13 @@
         <v>50005</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="E5" s="6">
         <v>10</v>
@@ -1140,13 +1118,13 @@
         <v>50006</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E6" s="6">
         <v>15</v>
@@ -1217,25 +1195,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="6" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>23</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -1243,20 +1221,20 @@
         <v>60001</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>83</v>
+        <v>35</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="F2" s="6"/>
       <c r="G2" s="6" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1264,22 +1242,22 @@
         <v>60002</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1287,22 +1265,22 @@
         <v>60003</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1310,22 +1288,22 @@
         <v>60004</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>69</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>28</v>
+        <v>87</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1333,22 +1311,22 @@
         <v>60005</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>18</v>
+        <v>76</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="5" customFormat="1">
@@ -1356,22 +1334,22 @@
         <v>60006</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>25</v>
+        <v>92</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:7" s="5" customFormat="1">
@@ -1379,16 +1357,13 @@
         <v>60007</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C8" s="0" t="inlineStr">
-        <v/>
-        <is>
-          <t xml:space="preserve">Strengthen:100|StatModifier:AttackArea:50</t>
-        </is>
+        <v>23</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>84</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1396,16 +1371,16 @@
         <v>60008</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:7" s="7" customFormat="1">
@@ -1413,13 +1388,13 @@
         <v>60009</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:7" s="7" customFormat="1">
@@ -1427,17 +1402,17 @@
         <v>60010</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="E11" s="6"/>
       <c r="G11" s="7" t="s">
-        <v>87</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:7" s="8" customFormat="1">
@@ -1445,15 +1420,15 @@
         <v>60011</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
       <c r="G12" s="8" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:7" s="8" customFormat="1">
@@ -1461,22 +1436,22 @@
         <v>60012</v>
       </c>
       <c r="B13" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>15</v>
-      </c>
       <c r="D13" s="6" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>75</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1484,20 +1459,20 @@
         <v>60013</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>9</v>
+        <v>74</v>
       </c>
       <c r="E14" s="6">
         <v>-20</v>
       </c>
       <c r="F14" s="6"/>
       <c r="G14" s="6" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1505,20 +1480,20 @@
         <v>60014</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="E15" s="6">
         <v>50</v>
       </c>
       <c r="F15" s="6"/>
       <c r="G15" s="6" t="s">
-        <v>77</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1526,10 +1501,10 @@
         <v>60015</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="D16" s="6">
         <v>-50</v>
@@ -1538,10 +1513,10 @@
         <v>0</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:1">
@@ -1552,19 +1527,19 @@
         <v>60017</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1572,19 +1547,19 @@
         <v>60018</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>32</v>
+        <v>74</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-30</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" s="6" customFormat="1"/>

--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -265,7 +265,7 @@
     <t xml:space="preserve">StatModifier:AttackDamage:100|ScaleProjectile</t>
   </si>
   <si>
-    <t xml:space="preserve">RepeatAfterAttack:0.2:3|StatModifier:AttackInterval:40</t>
+    <t xml:space="preserve">RepeatAfterAttack:0.2:2|StatModifier:AttackInterval:40</t>
   </si>
   <si>
     <t xml:space="preserve">Strengthen:100|StatModifier:AttackArea:50</t>

--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="105">
   <si>
     <t xml:space="preserve">30</t>
   </si>
@@ -314,6 +314,21 @@
   </si>
   <si>
     <t xml:space="preserve">skill_projectile_prefab_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60099_Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ColdAirProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5:3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passive_60099_Desc</t>
   </si>
 </sst>
 </file>
@@ -1183,7 +1198,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.4"/>
   <cols>
     <col min="2" max="2" width="18.7265625" style="6" bestFit="1" customWidth="1"/>
@@ -1565,6 +1580,29 @@
     <row r="20" s="6" customFormat="1"/>
     <row r="21" s="6" customFormat="1"/>
     <row r="22" s="6" customFormat="1"/>
+    <row r="23">
+      <c r="A23" s="0">
+        <v>60099</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="C23" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="D23" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="E23" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="F23" s="0" t="s">
+        <v>103</v>
+      </c>
+      <c r="G23" s="0" t="s">
+        <v>104</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait"/>

--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="105">
   <si>
     <t xml:space="preserve">30</t>
   </si>
@@ -1594,7 +1594,7 @@
         <v>101</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>102</v>
+        <v>24</v>
       </c>
       <c r="F23" s="0" t="s">
         <v>103</v>

--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="101">
   <si>
     <t xml:space="preserve">30</t>
   </si>
@@ -314,6 +314,9 @@
   </si>
   <si>
     <t xml:space="preserve">skill_projectile_prefab_id</t>
+  </si>
+  <si>
+    <t>TargetCount:100</t>
   </si>
 </sst>
 </file>
@@ -1468,9 +1471,11 @@
         <v>74</v>
       </c>
       <c r="E14" s="6">
-        <v>-20</v>
-      </c>
-      <c r="F14" s="6"/>
+        <v>-30</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="G14" s="6" t="s">
         <v>49</v>
       </c>

--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -1230,12 +1230,14 @@
         <v>71</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="F2" s="6"/>
+      <c r="F2" s="6">
+        <v>1.3</v>
+      </c>
       <c r="G2" s="6" t="s">
         <v>55</v>
       </c>

--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="102">
   <si>
     <t xml:space="preserve">30</t>
   </si>
@@ -317,6 +317,9 @@
   </si>
   <si>
     <t>TargetCount:100</t>
+  </si>
+  <si>
+    <t>AttackArea:-30:AttackRange:50</t>
   </si>
 </sst>
 </file>
@@ -1276,13 +1279,13 @@
         <v>80</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>5</v>
+        <v>69</v>
+      </c>
+      <c r="E4" s="3">
+        <v>50</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>33</v>
+        <v>101</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>30</v>

--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -1413,12 +1413,17 @@
         <v>50</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="E11" s="6"/>
+        <v>69</v>
+      </c>
+      <c r="E11" s="6">
+        <v>100</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>78</v>
+      </c>
       <c r="G11" s="7" t="s">
         <v>38</v>
       </c>

--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="103">
   <si>
     <t xml:space="preserve">30</t>
   </si>
@@ -320,6 +320,9 @@
   </si>
   <si>
     <t>AttackArea:-30:AttackRange:50</t>
+  </si>
+  <si>
+    <t>KnockbackOnHit</t>
   </si>
 </sst>
 </file>
@@ -1374,23 +1377,6 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="7">
-        <v>60008</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7" t="s">
-        <v>52</v>
-      </c>
-    </row>
     <row r="10" spans="1:7" s="7" customFormat="1">
       <c r="A10" s="7">
         <v>60009</v>
@@ -1399,7 +1385,13 @@
         <v>40</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>85</v>
+        <v>102</v>
+      </c>
+      <c r="D10" s="3">
+        <v>2</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0.3</v>
       </c>
       <c r="G10" s="7" t="s">
         <v>29</v>
@@ -1490,27 +1482,6 @@
         <v>49</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="6">
-        <v>60014</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="E15" s="6">
-        <v>50</v>
-      </c>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
     <row r="16" spans="1:7">
       <c r="A16" s="6">
         <v>60015</v>
@@ -1555,26 +1526,6 @@
       </c>
       <c r="G18" s="6" t="s">
         <v>39</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="6">
-        <v>60018</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="E19" s="6">
-        <v>-30</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="20" s="6" customFormat="1"/>

--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -265,7 +265,7 @@
     <t xml:space="preserve">StatModifier:AttackDamage:100|ScaleProjectile</t>
   </si>
   <si>
-    <t xml:space="preserve">RepeatAfterAttack:0.2:2|StatModifier:AttackInterval:40</t>
+    <t xml:space="preserve">StatModifier:AttackCount:2:AttackInterval:30</t>
   </si>
   <si>
     <t xml:space="preserve">Strengthen:100|StatModifier:AttackArea:50</t>
@@ -316,7 +316,7 @@
     <t xml:space="preserve">skill_projectile_prefab_id</t>
   </si>
   <si>
-    <t>TargetCount:100</t>
+    <t>TargetCount:2</t>
   </si>
   <si>
     <t>AttackArea:-30:AttackRange:50</t>

--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -1230,7 +1230,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Strengthen:100|StatModifier:AttackArea:50</t>
+          <t>Strengthen:100|StatModifier:AttackRange:50</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>AttackArea</t>
+          <t>AttackRange</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">

--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -1065,14 +1065,12 @@
           <t>AttackRange</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="E3" s="3" t="n">
+        <v>65</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>AttackArea:50</t>
+          <t>AttackArea:65</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -1101,11 +1099,11 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>AttackArea:-30:AttackRange:50</t>
+          <t>AttackArea:-30:AttackRange:65</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1133,10 +1131,8 @@
           <t>AttackDamage</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="E5" s="2" t="n">
+        <v>190</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -1230,7 +1226,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Strengthen:100|StatModifier:AttackRange:50</t>
+          <t>Strengthen:300|StatModifier:AttackRange:60</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -1286,11 +1282,11 @@
         </is>
       </c>
       <c r="E11" s="6" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>AttackArea:50</t>
+          <t>AttackArea:65</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
@@ -1310,7 +1306,7 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>StatModifier:AttackCount:2:AttackInterval:30</t>
+          <t>StatModifier:AttackCount:2:AttackInterval:40</t>
         </is>
       </c>
       <c r="D12" s="6" t="n"/>
@@ -1340,14 +1336,12 @@
           <t>AttackArea</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
+      <c r="E13" s="6" t="n">
+        <v>125</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>AttackDamage:50</t>
+          <t>AttackDamage:120</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
@@ -1376,7 +1370,7 @@
         </is>
       </c>
       <c r="E14" s="6" t="n">
-        <v>-30</v>
+        <v>-50</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
@@ -1465,7 +1459,7 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>StatModifier:AttackDamage:80:AttackInterval:33.3:AttackArea:70|ScaleProjectile:1.3</t>
+          <t>StatModifier:AttackDamage:230:AttackInterval:30:AttackArea:110|ScaleProjectile:1.3</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
@@ -1523,10 +1517,8 @@
           <t>AttackRange</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="E21" s="6" t="n">
+        <v>65</v>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>

--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -668,7 +668,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L9"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.4" outlineLevelCol="0"/>
   <cols>
     <col width="20.2109375" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
     <col width="12.28515625" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
@@ -966,8 +966,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.4"/>
+  <dimension ref="A1:G26"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.4" outlineLevelCol="0"/>
   <cols>
     <col width="18.7265625" bestFit="1" customWidth="1" style="6" min="2" max="2"/>
     <col width="19.0703125" bestFit="1" customWidth="1" style="6" min="3" max="3"/>
@@ -1235,7 +1235,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10" customFormat="1" s="7">
       <c r="A10" s="7" t="n">
         <v>60009</v>
@@ -1383,7 +1382,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="6" t="n">
         <v>60015</v>
@@ -1531,7 +1529,116 @@
         </is>
       </c>
     </row>
-    <row r="22" customFormat="1" s="6"/>
+    <row r="22" customFormat="1" s="6">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>60021</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Passive_60021_Name</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>KnockbackOnHit:2:0.15|StatModifier:AttackInterval:20</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>Passive_60021_Desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>60022</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Passive_60022_Name</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>SlowOnHit:30:0.5</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>Passive_60022_Desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>60023</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Passive_60023_Name</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>SweepAttack:0.4|StatModifier:AttackDamage:-60</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>Passive_60023_Desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>60024</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Passive_60024_Name</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>DischargeEveryN:5:200:1</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>Passive_60024_Desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>60025</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>Passive_60025_Name</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>StatModifier:AttackDamage:150:AttackInterval:30|StunDuration:0.5</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>Passive_60025_Desc</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="0"/>

--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -668,7 +668,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L9"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.4" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.4"/>
   <cols>
     <col width="20.2109375" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
     <col width="12.28515625" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
@@ -967,7 +967,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G26"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.4" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.4"/>
   <cols>
     <col width="18.7265625" bestFit="1" customWidth="1" style="6" min="2" max="2"/>
     <col width="19.0703125" bestFit="1" customWidth="1" style="6" min="3" max="3"/>
@@ -1393,20 +1393,12 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>RapidBombard</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>-50</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>2:10:7</t>
-        </is>
-      </c>
+          <t>StatModifier:AttackInterval:-50|RapidBombard:10:7</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
       <c r="G16" s="6" t="inlineStr">
         <is>
           <t>Passive_60015_Desc</t>

--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>SweepAttack:0.4|StatModifier:AttackDamage:-60</t>
+          <t>SweepAttack:0.8|StatModifier:AttackInterval:50</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">

--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -1534,7 +1534,7 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>KnockbackOnHit:2:0.15|StatModifier:AttackInterval:20</t>
+          <t>KnockbackOnHit:2:0.15|StatModifier:AttackDamage:-10</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>SweepAttack:0.8|StatModifier:AttackInterval:50</t>
+          <t>SweepAttack:0.8|StatModifier:AttackInterval:75</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">

--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="F2" s="6" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
@@ -1066,11 +1066,11 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>AttackArea:65</t>
+          <t>AttackArea:35</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -1098,12 +1098,12 @@
           <t>AttackDamage</t>
         </is>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>120</v>
+      <c r="E4" t="n">
+        <v>100</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>AttackArea:-30:AttackRange:65</t>
+          <t>AttackArea:-30:AttackRange:35</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1131,8 +1131,8 @@
           <t>AttackDamage</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>190</v>
+      <c r="E5" t="n">
+        <v>320</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -1244,16 +1244,10 @@
           <t>Passive_60009_Name</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>KnockbackOnHit</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>0.3</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>KnockbackOnHit:2:0.3|StatModifier:AttackDamage:60</t>
+        </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
@@ -1303,9 +1297,9 @@
           <t>Passive_60011_Name</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>StatModifier:AttackCount:2:AttackInterval:40</t>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>StatModifier:AttackCount:1:AttackInterval:40</t>
         </is>
       </c>
       <c r="D12" s="6" t="n"/>
@@ -1335,12 +1329,12 @@
           <t>AttackArea</t>
         </is>
       </c>
-      <c r="E13" s="6" t="n">
-        <v>125</v>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>AttackDamage:120</t>
+      <c r="E13" t="n">
+        <v>35</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>AttackDamage:30</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
@@ -1368,12 +1362,12 @@
           <t>AttackInterval</t>
         </is>
       </c>
-      <c r="E14" s="6" t="n">
-        <v>-50</v>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>TargetCount:2</t>
+      <c r="E14" t="n">
+        <v>-30</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>TargetCount:1</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
@@ -1449,7 +1443,7 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>StatModifier:AttackDamage:230:AttackInterval:30:AttackArea:110|ScaleProjectile:1.3</t>
+          <t>StatModifier:AttackDamage:230:AttackInterval:30:AttackArea:55|ScaleProjectile:1.3</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
@@ -1507,12 +1501,12 @@
           <t>AttackRange</t>
         </is>
       </c>
-      <c r="E21" s="6" t="n">
-        <v>65</v>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>SlowRate:10</t>
+      <c r="E21" t="n">
+        <v>60</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>SlowRate:10:AttackDamage:70</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
@@ -1532,9 +1526,9 @@
           <t>Passive_60021_Name</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>KnockbackOnHit:2:0.15|StatModifier:AttackDamage:-10</t>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>KnockbackOnHit:2:0.15|StatModifier:AttackDamage:100</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
@@ -1554,9 +1548,9 @@
           <t>Passive_60022_Name</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>SlowOnHit:30:0.5</t>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SlowOnHit:30:0.5|StatModifier:AttackDamage:80</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
@@ -1576,9 +1570,9 @@
           <t>Passive_60023_Name</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>SweepAttack:0.8|StatModifier:AttackInterval:75</t>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SweepAttack:0.8|StatModifier:AttackInterval:80</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
@@ -1598,9 +1592,9 @@
           <t>Passive_60024_Name</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>DischargeEveryN:5:200:1</t>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>DischargeEveryN:5:120:1</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
@@ -1620,9 +1614,9 @@
           <t>Passive_60025_Name</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>StatModifier:AttackDamage:150:AttackInterval:30|StunDuration:0.5</t>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>StatModifier:AttackDamage:250:AttackInterval:30|StunDuration:0.5</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">

--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -1204,9 +1204,9 @@
           <t>ExplosionProjectile</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>-1:0.5:0.3</t>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-1:1.0:0.3|StatModifier:AttackDamage:150</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -1224,9 +1224,9 @@
           <t>Passive_60007_Name</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Strengthen:300|StatModifier:AttackRange:60</t>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Strengthen:120|StatModifier:AttackRange:40</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">

--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -966,7 +966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.4"/>
   <cols>
     <col width="18.7265625" bestFit="1" customWidth="1" style="6" min="2" max="2"/>
@@ -1012,6 +1012,11 @@
           <t>description</t>
         </is>
       </c>
+      <c r="H1" s="6" t="inlineStr">
+        <is>
+          <t>unlock_condition</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="n">
@@ -1045,6 +1050,11 @@
           <t>Passive_60001_Desc</t>
         </is>
       </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>Attacks&gt;=1000</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
@@ -1078,6 +1088,11 @@
           <t>Passive_60002_Desc</t>
         </is>
       </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>Kills&gt;=350</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -1098,7 +1113,7 @@
           <t>AttackDamage</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="6" t="n">
         <v>100</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -1109,6 +1124,11 @@
       <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Passive_60003_Desc</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>AttackDamage&gt;=24</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1151,7 @@
           <t>AttackDamage</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="6" t="n">
         <v>320</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1142,6 +1162,11 @@
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Passive_60004_Desc</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>Slows&gt;=300</t>
         </is>
       </c>
     </row>
@@ -1204,14 +1229,19 @@
           <t>ExplosionProjectile</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>-1:1.0:0.3|StatModifier:AttackDamage:150</t>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>-1:1.0:0.3|StatModifier:AttackDamage:60</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Passive_60006_Desc</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Attacks&gt;=120</t>
         </is>
       </c>
     </row>
@@ -1224,9 +1254,9 @@
           <t>Passive_60007_Name</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Strengthen:120|StatModifier:AttackRange:40</t>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Strengthen:60|StatModifier:AttackRange:25</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -1234,7 +1264,13 @@
           <t>Passive_60007_Desc</t>
         </is>
       </c>
-    </row>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Kills&gt;=300</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10" customFormat="1" s="7">
       <c r="A10" s="7" t="n">
         <v>60009</v>
@@ -1244,7 +1280,7 @@
           <t>Passive_60009_Name</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>KnockbackOnHit:2:0.3|StatModifier:AttackDamage:60</t>
         </is>
@@ -1252,6 +1288,11 @@
       <c r="G10" s="7" t="inlineStr">
         <is>
           <t>Passive_60009_Desc</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Attacks&gt;=800</t>
         </is>
       </c>
     </row>
@@ -1287,6 +1328,11 @@
           <t>Passive_60010_Desc</t>
         </is>
       </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>DamageDealt&gt;=25000</t>
+        </is>
+      </c>
     </row>
     <row r="12" customFormat="1" s="8">
       <c r="A12" s="8" t="n">
@@ -1297,7 +1343,7 @@
           <t>Passive_60011_Name</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>StatModifier:AttackCount:1:AttackInterval:40</t>
         </is>
@@ -1309,6 +1355,11 @@
           <t>Passive_60011_Desc</t>
         </is>
       </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Attacks&gt;=300</t>
+        </is>
+      </c>
     </row>
     <row r="13" customFormat="1" s="8">
       <c r="A13" s="8" t="n">
@@ -1329,10 +1380,10 @@
           <t>AttackArea</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>AttackDamage:30</t>
         </is>
@@ -1340,6 +1391,11 @@
       <c r="G13" s="8" t="inlineStr">
         <is>
           <t>Passive_60012_Desc</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>AttackDamage&gt;=100</t>
         </is>
       </c>
     </row>
@@ -1362,10 +1418,10 @@
           <t>AttackInterval</t>
         </is>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="6" t="n">
         <v>-30</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>TargetCount:1</t>
         </is>
@@ -1375,7 +1431,13 @@
           <t>Passive_60013_Desc</t>
         </is>
       </c>
-    </row>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>Stuns&gt;=400</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="6" t="n">
         <v>60015</v>
@@ -1431,6 +1493,11 @@
           <t>Passive_60017_Desc</t>
         </is>
       </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>AttackDamage&gt;=100</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
@@ -1451,6 +1518,11 @@
           <t>Passive_60018_Desc</t>
         </is>
       </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>DamageDealt&gt;=25000</t>
+        </is>
+      </c>
     </row>
     <row r="20" customFormat="1" s="6">
       <c r="A20" s="6" t="n">
@@ -1481,6 +1553,11 @@
           <t>Passive_60019_Desc</t>
         </is>
       </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>Kills&gt;=400</t>
+        </is>
+      </c>
     </row>
     <row r="21" customFormat="1" s="6">
       <c r="A21" s="6" t="n">
@@ -1501,10 +1578,10 @@
           <t>AttackRange</t>
         </is>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <t>SlowRate:10:AttackDamage:70</t>
         </is>
@@ -1512,6 +1589,11 @@
       <c r="G21" s="6" t="inlineStr">
         <is>
           <t>Passive_60020_Desc</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>Slows&gt;=650</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1608,7 @@
           <t>Passive_60021_Name</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>KnockbackOnHit:2:0.15|StatModifier:AttackDamage:100</t>
         </is>
@@ -1534,6 +1616,11 @@
       <c r="G22" s="6" t="inlineStr">
         <is>
           <t>Passive_60021_Desc</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>Kills&gt;=600</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1635,7 @@
           <t>Passive_60022_Name</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>SlowOnHit:30:0.5|StatModifier:AttackDamage:80</t>
         </is>
@@ -1556,6 +1643,11 @@
       <c r="G23" s="6" t="inlineStr">
         <is>
           <t>Passive_60022_Desc</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>DamageDealt&gt;=40000</t>
         </is>
       </c>
     </row>
@@ -1570,7 +1662,7 @@
           <t>Passive_60023_Name</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>SweepAttack:0.8|StatModifier:AttackInterval:80</t>
         </is>
@@ -1578,6 +1670,11 @@
       <c r="G24" s="6" t="inlineStr">
         <is>
           <t>Passive_60023_Desc</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>DamageDealt&gt;=80000</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1689,7 @@
           <t>Passive_60024_Name</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>DischargeEveryN:5:120:1</t>
         </is>
@@ -1600,6 +1697,11 @@
       <c r="G25" s="6" t="inlineStr">
         <is>
           <t>Passive_60024_Desc</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>Stuns&gt;=900</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1716,7 @@
           <t>Passive_60025_Name</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>StatModifier:AttackDamage:250:AttackInterval:30|StunDuration:0.5</t>
         </is>
@@ -1622,6 +1724,11 @@
       <c r="G26" s="6" t="inlineStr">
         <is>
           <t>Passive_60025_Desc</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>AttackDamage&gt;=30</t>
         </is>
       </c>
     </row>

--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -1385,7 +1385,7 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>AttackDamage:30</t>
+          <t>AttackDamage:20</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">

--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -1076,11 +1076,11 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>AttackArea:35</t>
+          <t>AttackArea:25</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -1114,11 +1114,11 @@
         </is>
       </c>
       <c r="E4" s="6" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>AttackArea:-30:AttackRange:35</t>
+          <t>AttackArea:-30:AttackRange:25</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1143,22 +1143,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>StatModifier</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>AttackDamage</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>320</v>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>SlowRate:20</t>
-        </is>
-      </c>
+          <t>StatModifier:SlowRate:15|SlowCap:15</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Passive_60004_Desc</t>
@@ -1282,7 +1272,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>KnockbackOnHit:2:0.3|StatModifier:AttackDamage:60</t>
+          <t>KnockbackOnHit:2:0.3|StatModifier:AttackDamage:30</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
@@ -1316,11 +1306,11 @@
         </is>
       </c>
       <c r="E11" s="6" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>AttackArea:65</t>
+          <t>AttackArea:25</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
@@ -1381,11 +1371,11 @@
         </is>
       </c>
       <c r="E13" s="6" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>AttackDamage:20</t>
+          <t>AttackDamage:30</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
@@ -1510,7 +1500,7 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>StatModifier:AttackDamage:230:AttackInterval:30:AttackArea:55|ScaleProjectile:1.3</t>
+          <t>StatModifier:AttackDamage:50:AttackInterval:30:AttackArea:25|ScaleProjectile:1.3</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
@@ -1579,11 +1569,11 @@
         </is>
       </c>
       <c r="E21" s="6" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>SlowRate:10:AttackDamage:70</t>
+          <t>SlowRate:10:AttackDamage:25</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
@@ -1610,7 +1600,7 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>KnockbackOnHit:2:0.15|StatModifier:AttackDamage:100</t>
+          <t>KnockbackOnHit:2:0.15|StatModifier:AttackDamage:30</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
@@ -1637,7 +1627,7 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>SlowOnHit:30:0.5|StatModifier:AttackDamage:80</t>
+          <t>SlowOnHit:30:0.5|StatModifier:AttackDamage:30</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
@@ -1718,7 +1708,7 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>StatModifier:AttackDamage:250:AttackInterval:30|StunDuration:0.5</t>
+          <t>StatModifier:TargetCount:-2:AttackDamage:100|StunDuration:0.7</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">

--- a/Assets/02_Resources/Data/TrainSkillData.xlsx
+++ b/Assets/02_Resources/Data/TrainSkillData.xlsx
@@ -1260,7 +1260,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10" customFormat="1" s="7">
       <c r="A10" s="7" t="n">
         <v>60009</v>
@@ -1427,7 +1426,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="6" t="n">
         <v>60015</v>
@@ -1439,7 +1437,7 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>StatModifier:AttackInterval:-50|RapidBombard:10:7</t>
+          <t>StatModifier:AttackInterval:-150|RapidBombard</t>
         </is>
       </c>
       <c r="D16" s="6" t="n"/>
@@ -1450,6 +1448,11 @@
           <t>Passive_60015_Desc</t>
         </is>
       </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Attacks&gt;=150</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
@@ -1470,7 +1473,7 @@
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
